--- a/Equity/output/daily/SwingStocks_Mon_26th Oct.xlsx
+++ b/Equity/output/daily/SwingStocks_Mon_26th Oct.xlsx
@@ -565,7 +565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 23-Oct-2026 16:45 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
+          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 25-Oct-2026 21:21 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
         <v>71</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>4</v>
@@ -739,7 +739,7 @@
         <v>2257.35</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>2145.129579863279</v>
+        <v>2145.129579863428</v>
       </c>
       <c r="O5" s="9" t="n">
         <v>2391.45</v>
@@ -851,7 +851,7 @@
       <c r="G10" s="14" t="n"/>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>Risk flag: Extended &gt;7% above EMA20, Big 1D spike, Negative headline - check news | Too few past cases to know Hist Hit 7%</t>
+          <t>Risk flag: Extended &gt;7% above EMA20, Big 1D spike | Too few past cases to know Hist Hit 7%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 23-Oct-2026 16:45 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
+          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 25-Oct-2026 21:21 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
         <v>8</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>25.28574062184137</v>
+        <v>25.28650854698138</v>
       </c>
       <c r="Y5" s="8" t="n">
         <v>66.7038465474425</v>
@@ -1354,11 +1354,7 @@
       <c r="AE5" s="8" t="n">
         <v>-2.760252365930604</v>
       </c>
-      <c r="AF5" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+      <c r="AF5" s="6" t="inlineStr"/>
       <c r="AG5" s="6" t="inlineStr"/>
       <c r="AH5" s="6" t="inlineStr">
         <is>
@@ -1372,14 +1368,10 @@
       </c>
       <c r="AJ5" s="7" t="inlineStr">
         <is>
-          <t>Extended &gt;7% above EMA20 | Big 1D spike | Negative headline - check news</t>
-        </is>
-      </c>
-      <c r="AK5" s="7" t="inlineStr">
-        <is>
-          <t>[19 Oct 2026] Cyient DLM plunges 24% in two days; what's making the Street nervous? - Business Standard | [20 Oct 2026] Cyient (NSEI:CYIENT) Stock Forecast &amp; Analyst Predictions - Simply Wall Street | [22 Oct 2026] CYIENT: Revenue advanced, acquisitions expanded the portfolio, and ₹12 per share was declared as interim dividend - TradingView | [22 Oct 2026] Cyient Limited Reports Earnings Results for the Second Quarter and Six Months Ended September 30, 2026 - www.marketscreener.com</t>
-        </is>
-      </c>
+          <t>Extended &gt;7% above EMA20 | Big 1D spike</t>
+        </is>
+      </c>
+      <c r="AK5" s="7" t="inlineStr"/>
       <c r="AL5" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -1465,7 +1457,7 @@
         <v>16</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>4.717225503879559</v>
+        <v>4.717267838361655</v>
       </c>
       <c r="Y6" s="8" t="n">
         <v>62.73981784745713</v>
@@ -1488,11 +1480,7 @@
       <c r="AE6" s="8" t="n">
         <v>-17.36386441258447</v>
       </c>
-      <c r="AF6" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+      <c r="AF6" s="6" t="inlineStr"/>
       <c r="AG6" s="6" t="inlineStr"/>
       <c r="AH6" s="6" t="inlineStr">
         <is>
@@ -1509,11 +1497,7 @@
           <t>Big 1D spike | Weak trend (ADX&lt;20)</t>
         </is>
       </c>
-      <c r="AK6" s="7" t="inlineStr">
-        <is>
-          <t>[17 Oct 2026] Kolte-Patil Developers reports record H1 sales of INR 1,636 crore - Prop News Time</t>
-        </is>
-      </c>
+      <c r="AK6" s="7" t="inlineStr"/>
       <c r="AL6" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -1550,7 +1534,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -1570,10 +1554,10 @@
         <v>4877.075</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>4578.714948623475</v>
+        <v>4578.714948623476</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>5.465641184293081</v>
+        <v>5.465641184293062</v>
       </c>
       <c r="O7" s="9" t="n">
         <v>5182.4808</v>
@@ -1582,10 +1566,10 @@
         <v>5327.784</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>1.280728054398504</v>
+        <v>1.280728054398509</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>1.829611506283574</v>
+        <v>1.82961150628358</v>
       </c>
       <c r="S7" s="5" t="n">
         <v>3</v>
@@ -1606,13 +1590,13 @@
         <v>1.886923235350515</v>
       </c>
       <c r="Y7" s="8" t="n">
-        <v>62.38466863942166</v>
+        <v>62.38466863942168</v>
       </c>
       <c r="Z7" s="8" t="n">
-        <v>14.69677073754477</v>
+        <v>14.69677073753119</v>
       </c>
       <c r="AA7" s="8" t="n">
-        <v>3.095482519080337</v>
+        <v>3.09548251908033</v>
       </c>
       <c r="AB7" s="8" t="n">
         <v>4.195366050327309</v>
@@ -1626,11 +1610,7 @@
       <c r="AE7" s="8" t="n">
         <v>-5.087558899916401</v>
       </c>
-      <c r="AF7" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+      <c r="AF7" s="6" t="inlineStr"/>
       <c r="AG7" s="6" t="inlineStr"/>
       <c r="AH7" s="6" t="inlineStr">
         <is>
@@ -1647,11 +1627,7 @@
           <t>RELAXED smallcap | Weak trend (ADX&lt;20)</t>
         </is>
       </c>
-      <c r="AK7" s="7" t="inlineStr">
-        <is>
-          <t>[17 Oct 2026] CRISIL: Stable Financials And Interim Dividend Will Support Balanced Outlook - Simply Wall Street | [19 Oct 2026] CRISIL sets October 23 results date: INR 5,000 target for CRISIL stock - AD HOC NEWS | [18 Oct 2026] 10 Stocks Down 30–50% From ATH With Strong Profit Growth - Trade Brains</t>
-        </is>
-      </c>
+      <c r="AK7" s="7" t="inlineStr"/>
       <c r="AL7" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -1688,7 +1664,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
@@ -1708,10 +1684,10 @@
         <v>2257.35</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>2145.129579863279</v>
+        <v>2145.129579863428</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>4.021047880837644</v>
+        <v>4.021047880830951</v>
       </c>
       <c r="O8" s="9" t="n">
         <v>2391.45</v>
@@ -1720,10 +1696,10 @@
         <v>2458.5</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>1.740839753079938</v>
+        <v>1.740839753082836</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>2.486913932971336</v>
+        <v>2.486913932975475</v>
       </c>
       <c r="S8" s="5" t="n">
         <v>8</v>
@@ -1741,16 +1717,16 @@
         <v>71</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>2.075889578581005</v>
+        <v>2.075893436219113</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>63.91046213450047</v>
+        <v>63.91046213439159</v>
       </c>
       <c r="Z8" s="8" t="n">
-        <v>26.7715343630463</v>
+        <v>26.77153440604747</v>
       </c>
       <c r="AA8" s="8" t="n">
-        <v>2.23391548935425</v>
+        <v>2.233915489350526</v>
       </c>
       <c r="AB8" s="8" t="n">
         <v>2.764134480096248</v>
@@ -1764,11 +1740,7 @@
       <c r="AE8" s="8" t="n">
         <v>-1.285902707469566</v>
       </c>
-      <c r="AF8" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+      <c r="AF8" s="6" t="inlineStr"/>
       <c r="AG8" s="6" t="inlineStr"/>
       <c r="AH8" s="6" t="inlineStr">
         <is>
@@ -1781,11 +1753,7 @@
         </is>
       </c>
       <c r="AJ8" s="7" t="inlineStr"/>
-      <c r="AK8" s="7" t="inlineStr">
-        <is>
-          <t>[23 Oct 2026] Anand Rathi Wealth to host virtual investor meet on October 29, 2026 - scanx.trade | [23 Oct 2026] Anand Rathi Wealth (NSE:ANANDRATHI): What Is the Virtual Investor Meeting on 29 Oct 2026? - Kalkine India | [22 Oct 2026] Anand Rathi Wealth seeks approval for ₹1,200 crore related party deal - scanx.trade | [23 Oct 2026] ET Wealth Expo 2026: Day 2 to explore alternative investments, financial freedom and the changing face of - The Economic Times</t>
-        </is>
-      </c>
+      <c r="AK8" s="7" t="inlineStr"/>
       <c r="AL8" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -1875,7 +1843,7 @@
         <v>48</v>
       </c>
       <c r="X9" s="8" t="n">
-        <v>2.714630763344175</v>
+        <v>2.759638866068716</v>
       </c>
       <c r="Y9" s="8" t="n">
         <v>57.94247134176964</v>
@@ -1898,11 +1866,7 @@
       <c r="AE9" s="8" t="n">
         <v>-7.413431280837612</v>
       </c>
-      <c r="AF9" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+      <c r="AF9" s="6" t="inlineStr"/>
       <c r="AG9" s="6" t="inlineStr"/>
       <c r="AH9" s="6" t="inlineStr">
         <is>
@@ -1911,7 +1875,7 @@
       </c>
       <c r="AI9" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 2.7x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 73% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 2.8x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 73% of similar setups</t>
         </is>
       </c>
       <c r="AJ9" s="7" t="inlineStr">
@@ -1919,11 +1883,7 @@
           <t>Big 1D spike</t>
         </is>
       </c>
-      <c r="AK9" s="7" t="inlineStr">
-        <is>
-          <t>[19 Oct 2026] Tech picks: Indian Hotels among 5 stocks to buy for healthy returns in short term - The Economic Times</t>
-        </is>
-      </c>
+      <c r="AK9" s="7" t="inlineStr"/>
       <c r="AL9" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -2025,7 +1985,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 23-Oct-2026 16:45 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
+          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 25-Oct-2026 21:21 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2260,7 @@
         <v>18</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>1.955010967917732</v>
+        <v>1.955119595771021</v>
       </c>
       <c r="Y5" s="8" t="n">
         <v>62.12685793361327</v>
@@ -2323,11 +2283,7 @@
       <c r="AE5" s="8" t="n">
         <v>-2.873603515625001</v>
       </c>
-      <c r="AF5" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+      <c r="AF5" s="6" t="inlineStr"/>
       <c r="AG5" s="6" t="inlineStr"/>
       <c r="AH5" s="6" t="inlineStr">
         <is>
@@ -2340,11 +2296,7 @@
         </is>
       </c>
       <c r="AJ5" s="7" t="inlineStr"/>
-      <c r="AK5" s="7" t="inlineStr">
-        <is>
-          <t>[19 Oct 2026] IHCL and Oriental Hotels Announce Merger Deal - https://safariindia.com/ | [21 Oct 2026] Oriental Hotels Q2FY27 Results: Net profit down 8.2% to ₹1,162 lakh - scanx.trade | [21 Oct 2026] The Indian Hotels Company Limited (INDHOTEL) share price — eduinvesting - Howl.link</t>
-        </is>
-      </c>
+      <c r="AK5" s="7" t="inlineStr"/>
       <c r="AL5" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -2357,31 +2309,31 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Tech Mahindra Limited</t>
+          <t>The Indian Hotels Company Limited</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>NEAR BREAKOUT</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>WAIT - trigger not hit (buy above 1830.81)</t>
+          <t>BUY ZONE</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
@@ -2389,79 +2341,75 @@
         </is>
       </c>
       <c r="I6" s="9" t="n">
-        <v>1790</v>
+        <v>781.75</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1790</v>
+        <v>781.75</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1830.805941231521</v>
+        <v>773.9325</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>1856.411618731263</v>
+        <v>789.5675</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>1747.293128700748</v>
+        <v>743.8531973175888</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>5.224299880022096</v>
+        <v>4.847688222885993</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1972.66139458009</v>
+        <v>836.4725000000001</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>2027.969657979532</v>
+        <v>859.9250000000001</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>1.339892456550637</v>
+        <v>1.443987252924585</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>1.914132080786624</v>
+        <v>2.062838932749407</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>18436.08779981392</v>
+        <v>19543.75</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>36.66666666666666</v>
+        <v>12.82051282051282</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>16.66666666666666</v>
+        <v>5.128205128205128</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>0.8826152536772641</v>
+        <v>2.25349632206225</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>71.66286040465398</v>
+        <v>65.33309839806414</v>
       </c>
       <c r="Z6" s="8" t="n">
-        <v>27.18349324223552</v>
+        <v>19.92227355468049</v>
       </c>
       <c r="AA6" s="8" t="n">
-        <v>2.989312578542664</v>
+        <v>2.693160123825554</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>16.31869320425887</v>
+        <v>6.179966044142615</v>
       </c>
       <c r="AC6" s="8" t="n">
-        <v>16.00467509675574</v>
+        <v>7.969064730311093</v>
       </c>
       <c r="AD6" s="8" t="n">
-        <v>19.44355925081037</v>
+        <v>9.304832090694115</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>-2.981029810298108</v>
-      </c>
-      <c r="AF6" s="6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
+        <v>-1.62335921698038</v>
+      </c>
+      <c r="AF6" s="6" t="inlineStr"/>
       <c r="AG6" s="6" t="inlineStr"/>
       <c r="AH6" s="6" t="inlineStr">
         <is>
@@ -2470,19 +2418,15 @@
       </c>
       <c r="AI6" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 37% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 2.3x avg | OBV rising | Near 52W high | Beating NIFTY 1M</t>
         </is>
       </c>
       <c r="AJ6" s="7" t="inlineStr">
         <is>
-          <t>RSI&gt;70 (hot) | Extended &gt;7% above EMA20 | Volume below average</t>
-        </is>
-      </c>
-      <c r="AK6" s="7" t="inlineStr">
-        <is>
-          <t>[18 Oct 2026] ₹1,747 - That's What Analysts Think Tech Mahindra Limited (NSE:TECHM) Is Worth After These Results - Simply Wall Street | [20 Oct 2026] Tech Mahindra stock: Prabhudas Lilladher raises target to INR 1,910 - AD HOC NEWS | [20 Oct 2026] Tech Mahindra Limited (NSE:TECHM) Is About To Go Ex-Dividend, And It Pays A 2.9% Yield - Simply Wall Street | [16 Oct 2026] Tech Mahindra stock: Motilal Oswal targets Tech Mahindra stock at INR 1,950 - AD HOC NEWS</t>
-        </is>
-      </c>
+          <t>Weak trend (ADX&lt;20) | Low hist. +7% hit-rate</t>
+        </is>
+      </c>
+      <c r="AK6" s="7" t="inlineStr"/>
       <c r="AL6" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -2495,27 +2439,27 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>The Indian Hotels Company Limited</t>
+          <t>Tech Mahindra Limited</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>BUY ZONE</t>
+          <t>WAIT - trigger not hit (buy above 1830.81)</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
@@ -2527,79 +2471,75 @@
         </is>
       </c>
       <c r="I7" s="9" t="n">
-        <v>781.75</v>
+        <v>1790</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>781.75</v>
+        <v>1790</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>773.9325</v>
+        <v>1830.805941231521</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>789.5675</v>
+        <v>1856.411618731263</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>743.8531973175888</v>
+        <v>1747.293128647533</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>4.847688222885993</v>
+        <v>5.224299882908542</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>836.4725000000001</v>
+        <v>1972.66139458009</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>859.9250000000001</v>
+        <v>2027.969657979532</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>1.443987252924585</v>
+        <v>1.339892455810342</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>2.062838932749407</v>
+        <v>1.914132079729059</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>19543.75</v>
+        <v>18436.08779981392</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>12.82051282051282</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>5.128205128205128</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="X7" s="8" t="n">
-        <v>2.253394665971034</v>
+        <v>0.8826221586172116</v>
       </c>
       <c r="Y7" s="8" t="n">
-        <v>65.33309839806414</v>
+        <v>71.66286037085388</v>
       </c>
       <c r="Z7" s="8" t="n">
-        <v>19.92227355468049</v>
+        <v>27.18349290015075</v>
       </c>
       <c r="AA7" s="8" t="n">
-        <v>2.693160123825554</v>
+        <v>2.98931258019427</v>
       </c>
       <c r="AB7" s="8" t="n">
-        <v>6.179966044142615</v>
+        <v>16.31869320425887</v>
       </c>
       <c r="AC7" s="8" t="n">
-        <v>7.969064730311093</v>
+        <v>16.00467509675574</v>
       </c>
       <c r="AD7" s="8" t="n">
-        <v>9.304832090694115</v>
+        <v>19.44355925081037</v>
       </c>
       <c r="AE7" s="8" t="n">
-        <v>-1.62335921698038</v>
-      </c>
-      <c r="AF7" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+        <v>-2.981029810298108</v>
+      </c>
+      <c r="AF7" s="6" t="inlineStr"/>
       <c r="AG7" s="6" t="inlineStr"/>
       <c r="AH7" s="6" t="inlineStr">
         <is>
@@ -2608,19 +2548,15 @@
       </c>
       <c r="AI7" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 2.3x avg | OBV rising | Near 52W high | Beating NIFTY 1M</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 37% of similar setups</t>
         </is>
       </c>
       <c r="AJ7" s="7" t="inlineStr">
         <is>
-          <t>Weak trend (ADX&lt;20) | Low hist. +7% hit-rate | Negative headline - check news</t>
-        </is>
-      </c>
-      <c r="AK7" s="7" t="inlineStr">
-        <is>
-          <t>[18 Oct 2026] IHCL Fixes June 23 Record Date for ₹3.25 Dividend - scanx.trade | [22 Oct 2026] IHCL Share Price: Can Tata Group stock hit Rs 1,000 or fall to Rs 600? Bull-Bear scenarios explained - Zee Business | [21 Oct 2026] The Indian Hotels Company Limited Reports Earnings Results for the Second Quarter and Six Months Ended September 30, 2026 - www.marketscreener.com | [21 Oct 2026] Indian Hotels Q2FY27 Results: Net profit up 23% to ₹349 crore, misses estimates - scanx.trade</t>
-        </is>
-      </c>
+          <t>RSI&gt;70 (hot) | Extended &gt;7% above EMA20 | Volume below average</t>
+        </is>
+      </c>
+      <c r="AK7" s="7" t="inlineStr"/>
       <c r="AL7" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -2759,19 +2695,15 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Limited</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
-        </is>
-      </c>
+          <t>Shukra Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="6" t="inlineStr">
         <is>
           <t>EMA20 PULLBACK</t>
@@ -2791,100 +2723,92 @@
         </is>
       </c>
       <c r="I9" s="9" t="n">
-        <v>1475.599975585938</v>
+        <v>64.45999908447266</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1475.599975585938</v>
+        <v>64.45999908447266</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>1451.159048201276</v>
+        <v>64.09230332545485</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1482.977975463867</v>
+        <v>64.78229907989501</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>1379.685977172852</v>
+        <v>60.27009914398194</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>6.499999999999997</v>
+        <v>6.499999999999993</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>1578.891973876953</v>
+        <v>68.97219902038574</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>1623.159973144531</v>
+        <v>70.90599899291993</v>
       </c>
       <c r="Q9" s="8" t="n">
         <v>1.076923076923078</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>1.538461538461542</v>
+        <v>1.538461538461543</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>10</v>
+        <v>238</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>14755.99975585938</v>
+        <v>15341.47978210449</v>
       </c>
       <c r="U9" s="8" t="n">
-        <v>72.61904761904762</v>
+        <v>80</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>55.95238095238096</v>
+        <v>74</v>
       </c>
       <c r="W9" s="5" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="X9" s="8" t="n">
-        <v>2.040710687275184</v>
+        <v>2.386589512894483</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>53.04321535619313</v>
+        <v>55.23144585056946</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>21.35423501766923</v>
+        <v>56.04546748334655</v>
       </c>
       <c r="AA9" s="8" t="n">
-        <v>5.628073984472938</v>
+        <v>6.74265905769423</v>
       </c>
       <c r="AB9" s="8" t="n">
-        <v>6.005745372552984</v>
+        <v>10.018772685778</v>
       </c>
       <c r="AC9" s="8" t="n">
-        <v>21.29396186982777</v>
+        <v>99.47871438723736</v>
       </c>
       <c r="AD9" s="8" t="n">
-        <v>9.130611419104484</v>
+        <v>13.1436387323295</v>
       </c>
       <c r="AE9" s="8" t="n">
-        <v>-12.0357689665611</v>
-      </c>
-      <c r="AF9" s="6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
+        <v>-14.50928676394179</v>
+      </c>
+      <c r="AF9" s="6" t="inlineStr"/>
       <c r="AG9" s="6" t="inlineStr"/>
       <c r="AH9" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI9" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | Volume 2.0x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 73% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | ADX&gt;=25 strong trend | Volume 2.4x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 80% of similar setups</t>
         </is>
       </c>
       <c r="AJ9" s="7" t="inlineStr">
         <is>
-          <t>High volatility</t>
-        </is>
-      </c>
-      <c r="AK9" s="7" t="inlineStr">
-        <is>
-          <t>[23 Oct 2026] Two-fold jump in Q2 PAT, ₹25 dividend lift CPCL stock 5% in weak market - Business Standard | [22 Oct 2026] Chennai Petroleum Q2 results 2026: Navratna PSU declares ₹25 dividend, PAT jumps 212 % YoY - Check record date - Livemint | [22 Oct 2026] Chennai Petroleum Corporation Ltd declares interim dividend of Rs. 25 - EquityBulls | [22 Oct 2026] Chennai Petroleum Reports 212% Rise In Consolidated Net Profit To ₹2,247.03 Crore For September Quarter, - Free Press Journal</t>
-        </is>
-      </c>
+          <t>RELAXED smallcap | High volatility</t>
+        </is>
+      </c>
+      <c r="AK9" s="7" t="inlineStr"/>
       <c r="AL9" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -2974,7 +2898,7 @@
         <v>127</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>1.125335025597956</v>
+        <v>1.125491610737459</v>
       </c>
       <c r="Y10" s="8" t="n">
         <v>60.52354076074432</v>
@@ -2997,11 +2921,7 @@
       <c r="AE10" s="8" t="n">
         <v>-6.542222764756945</v>
       </c>
-      <c r="AF10" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+      <c r="AF10" s="6" t="inlineStr"/>
       <c r="AG10" s="6" t="inlineStr"/>
       <c r="AH10" s="6" t="inlineStr">
         <is>
@@ -3014,11 +2934,7 @@
         </is>
       </c>
       <c r="AJ10" s="7" t="inlineStr"/>
-      <c r="AK10" s="7" t="inlineStr">
-        <is>
-          <t>[19 Oct 2026] ICICI Bank Limited (ICICIBANK.NS) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada | [21 Oct 2026] HDFC Bank Limited (HDFCBANK.NS) stock price, news, quote and history - Yahoo Finance Singapore | [21 Oct 2026] Stock recommendations for 21 October from MarketSmith India - TradingView | [17 Oct 2026] South Indian Bank Revises Marginal Cost of Funds Based Lending Rates (MCLR) Effective October 20, 2026 - EquityBulls</t>
-        </is>
-      </c>
+      <c r="AK10" s="7" t="inlineStr"/>
       <c r="AL10" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -3031,12 +2947,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Krishana Phoschem Limited</t>
+          <t>Gandhar Oil Refinery (India) Limited</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
@@ -3051,7 +2967,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -3059,96 +2975,88 @@
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>199.6600036621094</v>
+        <v>293</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>199.6600036621094</v>
+        <v>293</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>197.8206052040397</v>
+        <v>288.7450518283894</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>200.6583036804199</v>
+        <v>294.465</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>186.6821034240723</v>
+        <v>273.955</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>6.499999999999999</v>
+        <v>6.499999999999987</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>213.6362039184571</v>
+        <v>313.51</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>219.6260040283203</v>
+        <v>322.3</v>
       </c>
       <c r="Q11" s="8" t="n">
         <v>1.076923076923079</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>1.538461538461539</v>
+        <v>1.538461538461542</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>15373.82028198242</v>
+        <v>15236</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>64.28571428571429</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>55.95238095238096</v>
+        <v>50</v>
       </c>
       <c r="W11" s="5" t="n">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="X11" s="8" t="n">
-        <v>1.24518685503169</v>
+        <v>1.589543501505834</v>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>54.03760708213146</v>
+        <v>55.28912551064992</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>22.35732119485644</v>
+        <v>23.63393790269302</v>
       </c>
       <c r="AA11" s="8" t="n">
-        <v>4.256860424415056</v>
+        <v>4.784448844035608</v>
       </c>
       <c r="AB11" s="8" t="n">
-        <v>5.333685279652012</v>
+        <v>8.901696076440846</v>
       </c>
       <c r="AC11" s="8" t="n">
-        <v>28.19261872366574</v>
+        <v>4.886134756224192</v>
       </c>
       <c r="AD11" s="8" t="n">
-        <v>8.458551326203512</v>
+        <v>12.02656212299235</v>
       </c>
       <c r="AE11" s="8" t="n">
-        <v>-7.56481311939381</v>
-      </c>
-      <c r="AF11" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+        <v>-6.539074960127589</v>
+      </c>
+      <c r="AF11" s="6" t="inlineStr"/>
       <c r="AG11" s="6" t="inlineStr"/>
       <c r="AH11" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI11" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 64% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | Volume 1.6x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 61% of similar setups</t>
         </is>
       </c>
       <c r="AJ11" s="7" t="inlineStr"/>
-      <c r="AK11" s="7" t="inlineStr">
-        <is>
-          <t>[20 Oct 2026] Krishana Phoschem (NSEI:KRISHANA) - Stock Analysis - Simply Wall Street | [17 Oct 2026] Canadian Phosphate Limited (CP8.AX) stock price, news, quote and history - Yahoo Finance UK</t>
-        </is>
-      </c>
+      <c r="AK11" s="7" t="inlineStr"/>
       <c r="AL11" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -3161,18 +3069,22 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Shukra Pharmaceuticals Limited</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr"/>
+          <t>SKY GOLD AND DIAMONDS LIMITED</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -3181,7 +3093,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -3189,100 +3101,92 @@
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>64.45999908447266</v>
+        <v>1046.849975585938</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>64.45999908447266</v>
+        <v>1046.849975585938</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>64.09230332545485</v>
+        <v>1036.381475830078</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>64.78229907989501</v>
+        <v>1057.318475341797</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>60.27009914398194</v>
+        <v>978.8047271728516</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>6.499999999999993</v>
+        <v>6.499999999999997</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>68.97219902038574</v>
+        <v>1120.129473876953</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>70.90599899291993</v>
+        <v>1151.534973144531</v>
       </c>
       <c r="Q12" s="8" t="n">
         <v>1.076923076923078</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>1.538461538461543</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>238</v>
+        <v>14</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>15341.47978210449</v>
+        <v>14655.89965820312</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>80</v>
+        <v>74.28571428571429</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>74</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="W12" s="5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>2.386415967260419</v>
+        <v>1.093507865595169</v>
       </c>
       <c r="Y12" s="8" t="n">
-        <v>55.23144585056946</v>
+        <v>76.38632884606807</v>
       </c>
       <c r="Z12" s="8" t="n">
-        <v>56.04546741086992</v>
+        <v>40.87138360524673</v>
       </c>
       <c r="AA12" s="8" t="n">
-        <v>6.74265905769423</v>
+        <v>4.530611325325584</v>
       </c>
       <c r="AB12" s="8" t="n">
-        <v>10.018772685778</v>
+        <v>30.44046994066991</v>
       </c>
       <c r="AC12" s="8" t="n">
-        <v>99.47871438723736</v>
+        <v>61.25230374334849</v>
       </c>
       <c r="AD12" s="8" t="n">
-        <v>13.1436387323295</v>
+        <v>33.56533598722142</v>
       </c>
       <c r="AE12" s="8" t="n">
-        <v>-14.50928676394179</v>
-      </c>
-      <c r="AF12" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+        <v>-3.422664999046143</v>
+      </c>
+      <c r="AF12" s="6" t="inlineStr"/>
       <c r="AG12" s="6" t="inlineStr"/>
       <c r="AH12" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI12" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | ADX&gt;=25 strong trend | Volume 2.4x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 80% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Near 52W high | Beating NIFTY 1M | Stock hit +7% in 15d 74% of similar setups</t>
         </is>
       </c>
       <c r="AJ12" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap | High volatility</t>
-        </is>
-      </c>
-      <c r="AK12" s="7" t="inlineStr">
-        <is>
-          <t>[21 Oct 2026] SHUKRA MEDTECH (NSEI:SHUKRAPHAR) - Stock Analysis - Simply Wall Street</t>
-        </is>
-      </c>
+          <t>RELAXED smallcap | RSI&gt;70 (hot) | Extended &gt;7% above EMA20</t>
+        </is>
+      </c>
+      <c r="AK12" s="7" t="inlineStr"/>
       <c r="AL12" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -3295,12 +3199,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>KRISHANA</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Gandhar Oil Refinery (India) Limited</t>
+          <t>Krishana Phoschem Limited</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr"/>
@@ -3315,7 +3219,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
@@ -3323,79 +3227,75 @@
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>293</v>
+        <v>199.6600036621094</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>293</v>
+        <v>199.6600036621094</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>288.7450518283894</v>
+        <v>197.8206052040397</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>294.465</v>
+        <v>200.6583036804199</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>273.955</v>
+        <v>186.6821034240723</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>6.499999999999987</v>
+        <v>6.499999999999999</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>313.51</v>
+        <v>213.6362039184571</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>322.3</v>
+        <v>219.6260040283203</v>
       </c>
       <c r="Q13" s="8" t="n">
         <v>1.076923076923079</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>1.538461538461542</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>15236</v>
+        <v>15373.82028198242</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>61.11111111111111</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>50</v>
+        <v>55.95238095238096</v>
       </c>
       <c r="W13" s="5" t="n">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="X13" s="8" t="n">
-        <v>1.589502479341174</v>
+        <v>1.245591049309489</v>
       </c>
       <c r="Y13" s="8" t="n">
-        <v>55.28912551064992</v>
+        <v>54.03760708213146</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>23.63393790269321</v>
+        <v>22.35732119485634</v>
       </c>
       <c r="AA13" s="8" t="n">
-        <v>4.784448844035608</v>
+        <v>4.256860424415056</v>
       </c>
       <c r="AB13" s="8" t="n">
-        <v>8.901696076440846</v>
+        <v>5.333685279652012</v>
       </c>
       <c r="AC13" s="8" t="n">
-        <v>4.886134756224192</v>
+        <v>28.19261872366574</v>
       </c>
       <c r="AD13" s="8" t="n">
-        <v>12.02656212299235</v>
+        <v>8.458551326203512</v>
       </c>
       <c r="AE13" s="8" t="n">
-        <v>-6.539074960127589</v>
-      </c>
-      <c r="AF13" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+        <v>-7.56481311939381</v>
+      </c>
+      <c r="AF13" s="6" t="inlineStr"/>
       <c r="AG13" s="6" t="inlineStr"/>
       <c r="AH13" s="6" t="inlineStr">
         <is>
@@ -3404,15 +3304,11 @@
       </c>
       <c r="AI13" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | Volume 1.6x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 61% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 64% of similar setups</t>
         </is>
       </c>
       <c r="AJ13" s="7" t="inlineStr"/>
-      <c r="AK13" s="7" t="inlineStr">
-        <is>
-          <t>[18 Oct 2026] Gandhar Oil Refinery Completes Punjab Property Sale for Rs. 1.61 Crores Under Regulation 30 - scanx.trade | [22 Oct 2026] Reliance Industries Limited (RELIANCE.NS) stock price, news, quote and history - Yahoo Finance Singapore | [22 Oct 2026] Gandhar Oil Refinery GANDHAR Share Capital Audit Q2 FY27 - Kalkine India | [19 Oct 2026] Gandhar Oil Refinery Q2 FY27 Earnings Call Scheduled 28 Oct - Kalkine India</t>
-        </is>
-      </c>
+      <c r="AK13" s="7" t="inlineStr"/>
       <c r="AL13" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -3425,27 +3321,27 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>MGEL</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Mangalam Global Enterprise Limited</t>
+          <t>Dhanlaxmi Bank Limited</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>NEAR BREAKOUT</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>WAIT - trigger not hit (buy above 17.52)</t>
+          <t>BUY ZONE</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -3453,100 +3349,92 @@
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>17.02000045776367</v>
+        <v>35.7599983215332</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>17.02000045776367</v>
+        <v>35.7599983215332</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>17.5175</v>
+        <v>35.40239833831787</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>17.7625</v>
+        <v>36.11759830474853</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>16.4934</v>
+        <v>33.43559843063355</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>6.499999999999996</v>
+        <v>6.499999999999993</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>18.8748</v>
+        <v>38.26319820404053</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>19.404</v>
+        <v>39.33599815368652</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>1.076923076923077</v>
+        <v>1.076923076923078</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>1.538461538461542</v>
+        <v>1.538461538461541</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>872</v>
+        <v>430</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>15382.08</v>
+        <v>15376.79927825928</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>64.28571428571429</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>50</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>1.1695111286998</v>
+        <v>0.8027997887424463</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>69.02241201590923</v>
+        <v>60.94981231881023</v>
       </c>
       <c r="Z14" s="8" t="n">
-        <v>24.63349883425135</v>
+        <v>27.0621664887438</v>
       </c>
       <c r="AA14" s="8" t="n">
-        <v>4.302788882543214</v>
+        <v>5.997910681626029</v>
       </c>
       <c r="AB14" s="8" t="n">
-        <v>9.6649481685398</v>
+        <v>22.54968453578221</v>
       </c>
       <c r="AC14" s="8" t="n">
-        <v>4.097859698237616</v>
+        <v>4.074498504985091</v>
       </c>
       <c r="AD14" s="8" t="n">
-        <v>12.7898142150913</v>
+        <v>25.67455058233371</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>-2.742854527064731</v>
-      </c>
-      <c r="AF14" s="6" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+        <v>-5.86997435748361</v>
+      </c>
+      <c r="AF14" s="6" t="inlineStr"/>
       <c r="AG14" s="6" t="inlineStr"/>
       <c r="AH14" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI14" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 64% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 42% of similar setups</t>
         </is>
       </c>
       <c r="AJ14" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap | Negative headline - check news</t>
-        </is>
-      </c>
-      <c r="AK14" s="7" t="inlineStr">
-        <is>
-          <t>[18 Oct 2026] Mangalam Global Enterprise (NSEI:MGEL) - Stock Analysis - Simply Wall Street | [22 Oct 2026] Mangalam Global Q2FY27 Results: Net profit falls 48% YoY to ₹9.30 crore - scanx.trade | [19 Oct 2026] Mangalam Global Enterprise (MGEL.NS) Holds Near ₹17.02 as ₹17.87 Resistance Comes Into Focus - KAMA Signal - https://www.siam.in/ | [21 Oct 2026] MGEL Reports 41.85% Growth in Q2 FY27 Profit Before Tax - Machine Maker</t>
-        </is>
-      </c>
+          <t>RELAXED smallcap | Extended &gt;7% above EMA20 | High volatility | Volume below average</t>
+        </is>
+      </c>
+      <c r="AK14" s="7" t="inlineStr"/>
       <c r="AL14" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -3559,18 +3447,22 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Dhanlaxmi Bank Limited</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr"/>
+          <t>Chennai Petroleum Corporation Limited</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>EMA20 PULLBACK</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -3579,7 +3471,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
@@ -3587,73 +3479,73 @@
         </is>
       </c>
       <c r="I15" s="9" t="n">
-        <v>35.7599983215332</v>
+        <v>1475.599975585938</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>35.7599983215332</v>
+        <v>1475.599975585938</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>35.40239833831787</v>
+        <v>1451.159048201276</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>36.11759830474853</v>
+        <v>1482.977975463867</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>33.43559843063355</v>
+        <v>1379.685977172852</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>6.499999999999993</v>
+        <v>6.499999999999997</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>38.26319820404053</v>
+        <v>1578.891973876953</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>39.33599815368652</v>
+        <v>1623.159973144531</v>
       </c>
       <c r="Q15" s="8" t="n">
         <v>1.076923076923078</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>1.538461538461541</v>
+        <v>1.538461538461542</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>430</v>
+        <v>10</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>15376.79927825928</v>
+        <v>14755.99975585938</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>42.10526315789473</v>
+        <v>72.61904761904762</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>5.263157894736842</v>
+        <v>55.95238095238096</v>
       </c>
       <c r="W15" s="5" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="X15" s="8" t="n">
-        <v>0.8027965940661571</v>
+        <v>2.041127583077954</v>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>60.94981231881023</v>
+        <v>53.04321535619313</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>27.0621664887438</v>
+        <v>21.35423501766923</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>5.997910681626029</v>
+        <v>5.628073984472938</v>
       </c>
       <c r="AB15" s="8" t="n">
-        <v>22.54968453578221</v>
+        <v>6.005745372552984</v>
       </c>
       <c r="AC15" s="8" t="n">
-        <v>4.074498504985091</v>
+        <v>21.29396186982777</v>
       </c>
       <c r="AD15" s="8" t="n">
-        <v>25.67455058233371</v>
+        <v>9.130611419104484</v>
       </c>
       <c r="AE15" s="8" t="n">
-        <v>-5.86997435748361</v>
+        <v>-12.0357689665611</v>
       </c>
       <c r="AF15" s="6" t="inlineStr"/>
       <c r="AG15" s="6" t="inlineStr"/>
@@ -3664,12 +3556,12 @@
       </c>
       <c r="AI15" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 42% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | Volume 2.0x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 73% of similar setups</t>
         </is>
       </c>
       <c r="AJ15" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap | Extended &gt;7% above EMA20 | High volatility | Volume below average</t>
+          <t>High volatility</t>
         </is>
       </c>
       <c r="AK15" s="7" t="inlineStr"/>
@@ -3685,31 +3577,27 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>MGEL</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>SKY GOLD AND DIAMONDS LIMITED</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Consumer Durables</t>
-        </is>
-      </c>
+          <t>Mangalam Global Enterprise Limited</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>BUY ZONE</t>
+          <t>WAIT - trigger not hit (buy above 17.52)</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
@@ -3717,79 +3605,75 @@
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>1046.849975585938</v>
+        <v>17.02000045776367</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1046.849975585938</v>
+        <v>17.02000045776367</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1036.381475830078</v>
+        <v>17.5175</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1057.318475341797</v>
+        <v>17.7625</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>978.8047271728516</v>
+        <v>16.4934</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>6.499999999999997</v>
+        <v>6.499999999999996</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>1120.129473876953</v>
+        <v>18.8748</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>1151.534973144531</v>
+        <v>19.404</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>1.076923076923078</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>1.538461538461539</v>
+        <v>1.538461538461542</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>14</v>
+        <v>872</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>14655.89965820312</v>
+        <v>15382.08</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>74.28571428571429</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>68.57142857142857</v>
+        <v>50</v>
       </c>
       <c r="W16" s="5" t="n">
         <v>70</v>
       </c>
       <c r="X16" s="8" t="n">
-        <v>1.093398314519418</v>
+        <v>1.1695111286998</v>
       </c>
       <c r="Y16" s="8" t="n">
-        <v>76.38632884606807</v>
+        <v>69.02241201590923</v>
       </c>
       <c r="Z16" s="8" t="n">
-        <v>40.87138360524673</v>
+        <v>24.63349883425135</v>
       </c>
       <c r="AA16" s="8" t="n">
-        <v>4.530611325325584</v>
+        <v>4.302788882543214</v>
       </c>
       <c r="AB16" s="8" t="n">
-        <v>30.44046994066991</v>
+        <v>9.6649481685398</v>
       </c>
       <c r="AC16" s="8" t="n">
-        <v>61.25230374334849</v>
+        <v>4.097859698237616</v>
       </c>
       <c r="AD16" s="8" t="n">
-        <v>33.56533598722142</v>
+        <v>12.7898142150913</v>
       </c>
       <c r="AE16" s="8" t="n">
-        <v>-3.422664999046143</v>
-      </c>
-      <c r="AF16" s="6" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+        <v>-2.742854527064731</v>
+      </c>
+      <c r="AF16" s="6" t="inlineStr"/>
       <c r="AG16" s="6" t="inlineStr"/>
       <c r="AH16" s="6" t="inlineStr">
         <is>
@@ -3798,19 +3682,15 @@
       </c>
       <c r="AI16" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Near 52W high | Beating NIFTY 1M | Stock hit +7% in 15d 74% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 64% of similar setups</t>
         </is>
       </c>
       <c r="AJ16" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap | RSI&gt;70 (hot) | Extended &gt;7% above EMA20 | Negative headline - check news</t>
-        </is>
-      </c>
-      <c r="AK16" s="7" t="inlineStr">
-        <is>
-          <t>[20 Oct 2026] Sky Gold and Diamonds Limited (SKYGOLD.NS) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada | [21 Oct 2026] Sky Gold &amp; Diamonds to acquire Purvi Gems to expand portfolio and strengthen jewellery business - The Retail Jeweller India | [22 Oct 2026] Sky Gold and Diamonds Plans Fund Raising via Eligible Securities - Sahi | [16 Oct 2026] Sky Gold and Diamonds SKYGOLD Internal Auditor Change October 2026 - Kalkine India</t>
-        </is>
-      </c>
+          <t>RELAXED smallcap</t>
+        </is>
+      </c>
+      <c r="AK16" s="7" t="inlineStr"/>
       <c r="AL16" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -3843,7 +3723,7 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
@@ -3896,7 +3776,7 @@
         <v>54</v>
       </c>
       <c r="X17" s="8" t="n">
-        <v>1.006830215370086</v>
+        <v>1.007296015434859</v>
       </c>
       <c r="Y17" s="8" t="n">
         <v>59.13343499000557</v>
@@ -3923,7 +3803,7 @@
       <c r="AG17" s="6" t="inlineStr"/>
       <c r="AH17" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI17" s="7" t="inlineStr">
@@ -3965,7 +3845,7 @@
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
@@ -4041,15 +3921,11 @@
       <c r="AE18" s="8" t="n">
         <v>-7.534246575342463</v>
       </c>
-      <c r="AF18" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+      <c r="AF18" s="6" t="inlineStr"/>
       <c r="AG18" s="6" t="inlineStr"/>
       <c r="AH18" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI18" s="7" t="inlineStr">
@@ -4062,11 +3938,7 @@
           <t>RELAXED smallcap</t>
         </is>
       </c>
-      <c r="AK18" s="7" t="inlineStr">
-        <is>
-          <t>[23 Oct 2026] Bombay Coated and Special Steels IPO Date, Review, Price, Allotment Details - IPO Watch</t>
-        </is>
-      </c>
+      <c r="AK18" s="7" t="inlineStr"/>
       <c r="AL18" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -4099,7 +3971,7 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -4169,15 +4041,11 @@
         <v>14.48908884817056</v>
       </c>
       <c r="AE19" s="6" t="inlineStr"/>
-      <c r="AF19" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+      <c r="AF19" s="6" t="inlineStr"/>
       <c r="AG19" s="6" t="inlineStr"/>
       <c r="AH19" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI19" s="7" t="inlineStr">
@@ -4190,11 +4058,7 @@
           <t>RELAXED smallcap | High volatility</t>
         </is>
       </c>
-      <c r="AK19" s="7" t="inlineStr">
-        <is>
-          <t>[18 Oct 2026] Singer India net profit turns positive in Q1FY27; revenue up 57% - scanx.trade</t>
-        </is>
-      </c>
+      <c r="AK19" s="7" t="inlineStr"/>
       <c r="AL19" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -4207,15 +4071,19 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>AAREYDRUGS</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Aarey Drugs &amp; Pharmaceuticals Limited</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr"/>
+          <t>Coforge Limited</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>EMA20 PULLBACK</t>
@@ -4227,95 +4095,103 @@
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I20" s="9" t="n">
-        <v>106.7300033569336</v>
+        <v>1900.5</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>106.7300033569336</v>
+        <v>1900.5</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>106.0287253175297</v>
+        <v>1880.723140871288</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>107.2636533737183</v>
+        <v>1910.0025</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>100.0074521255493</v>
+        <v>1828.013951416016</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>6.298651756715747</v>
+        <v>3.814051490870007</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>114.201103591919</v>
+        <v>2033.535</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>117.403003692627</v>
+        <v>2090.55</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>1.111348947421401</v>
+        <v>1.835318693718858</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>1.587641353459146</v>
+        <v>2.621883848169798</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>148</v>
+        <v>10</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>15796.04049682617</v>
+        <v>19005</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>69.6969696969697</v>
+        <v>32.5</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>48.48484848484848</v>
+        <v>5</v>
       </c>
       <c r="W20" s="5" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>1.229769527097014</v>
+        <v>1.642262016726502</v>
       </c>
       <c r="Y20" s="8" t="n">
-        <v>54.82663292184034</v>
+        <v>54.55287821241041</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>20.42492358220735</v>
+        <v>16.96824002509117</v>
       </c>
       <c r="AA20" s="8" t="n">
-        <v>4.753021505008639</v>
+        <v>3.314539344414698</v>
       </c>
       <c r="AB20" s="8" t="n">
-        <v>4.106522485095998</v>
+        <v>5.407653910149746</v>
       </c>
       <c r="AC20" s="8" t="n">
-        <v>38.25130515029611</v>
+        <v>32.29581811051689</v>
       </c>
       <c r="AD20" s="8" t="n">
-        <v>7.231388531647498</v>
+        <v>8.532519956701245</v>
       </c>
       <c r="AE20" s="8" t="n">
-        <v>-7.029616272036021</v>
+        <v>-5.971697708675194</v>
       </c>
       <c r="AF20" s="6" t="inlineStr"/>
-      <c r="AG20" s="6" t="inlineStr"/>
+      <c r="AG20" s="6" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
       <c r="AH20" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI20" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 70% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ20" s="7" t="inlineStr"/>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 1.6x avg | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 32% of similar setups</t>
+        </is>
+      </c>
+      <c r="AJ20" s="7" t="inlineStr">
+        <is>
+          <t>RELAXED smallcap | Weak trend (ADX&lt;20)</t>
+        </is>
+      </c>
       <c r="AK20" s="7" t="inlineStr"/>
       <c r="AL20" s="10" t="inlineStr">
         <is>
@@ -4329,22 +4205,18 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>SEJALLTD</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Coforge Limited</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
+          <t>Sejal Glass Limited</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr"/>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -4353,108 +4225,100 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>1900.5</v>
+        <v>845.4500122070312</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1900.5</v>
+        <v>845.4500122070312</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1880.723140871288</v>
+        <v>836.995512084961</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1910.0025</v>
+        <v>853.9045123291015</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>1828.013951416016</v>
+        <v>790.4957614135743</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>3.814051490870007</v>
+        <v>6.499999999999989</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>2033.535</v>
+        <v>904.6315130615235</v>
       </c>
       <c r="P21" s="9" t="n">
-        <v>2090.55</v>
+        <v>929.9950134277344</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>1.835318693718858</v>
+        <v>1.07692307692308</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>2.621883848169798</v>
+        <v>1.538461538461542</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>19005</v>
+        <v>15218.10021972656</v>
       </c>
       <c r="U21" s="8" t="n">
-        <v>32.5</v>
+        <v>40.42553191489361</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>5</v>
+        <v>27.65957446808511</v>
       </c>
       <c r="W21" s="5" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="X21" s="8" t="n">
-        <v>1.642165566809154</v>
+        <v>0.7908182112019209</v>
       </c>
       <c r="Y21" s="8" t="n">
-        <v>54.55287821242818</v>
+        <v>60.81441684378656</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>16.96824002595774</v>
+        <v>33.05681362018801</v>
       </c>
       <c r="AA21" s="8" t="n">
-        <v>3.314539344412542</v>
+        <v>7.828790512813259</v>
       </c>
       <c r="AB21" s="8" t="n">
-        <v>5.407653910149746</v>
+        <v>26.88729216512122</v>
       </c>
       <c r="AC21" s="8" t="n">
-        <v>32.29581811051689</v>
+        <v>9.984389070014643</v>
       </c>
       <c r="AD21" s="8" t="n">
-        <v>8.532519956701245</v>
+        <v>30.01215821167272</v>
       </c>
       <c r="AE21" s="8" t="n">
-        <v>-5.971697708675194</v>
-      </c>
-      <c r="AF21" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+        <v>-18.44795485411731</v>
+      </c>
+      <c r="AF21" s="6" t="inlineStr"/>
       <c r="AG21" s="6" t="inlineStr"/>
       <c r="AH21" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI21" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 1.6x avg | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 32% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 40% of similar setups</t>
         </is>
       </c>
       <c r="AJ21" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap | Weak trend (ADX&lt;20)</t>
-        </is>
-      </c>
-      <c r="AK21" s="7" t="inlineStr">
-        <is>
-          <t>[20 Oct 2026] Coforge Limited (COFORGE.NS) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada | [16 Oct 2026] Tata Consultancy Services Limited (TCS.BO) stock price, news, quote and history - Yahoo Finance Australia | [19 Oct 2026] Coforge schedules October 23 results call for Coforge stock - ad-hoc-news.de | [20 Oct 2026] HCL Technologies Limited (HCLTECH.NS) stock price, news, quote and history - Yahoo Finance UK</t>
-        </is>
-      </c>
+          <t>RELAXED smallcap | Extended &gt;7% above EMA20 | High volatility | Volume below average</t>
+        </is>
+      </c>
+      <c r="AK21" s="7" t="inlineStr"/>
       <c r="AL21" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -4467,18 +4331,18 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>SEJALLTD</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Sejal Glass Limited</t>
+          <t>Aarey Drugs &amp; Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>EMA20 PULLBACK</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -4487,7 +4351,7 @@
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
@@ -4495,100 +4359,88 @@
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>845.4500122070312</v>
+        <v>106.7300033569336</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>845.4500122070312</v>
+        <v>106.7300033569336</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>836.995512084961</v>
+        <v>106.0287253175297</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>853.9045123291015</v>
+        <v>107.2636533737183</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>790.4957614135743</v>
+        <v>100.0074521255493</v>
       </c>
       <c r="N22" s="8" t="n">
-        <v>6.499999999999989</v>
+        <v>6.298651756715747</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>904.6315130615235</v>
+        <v>114.201103591919</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>929.9950134277344</v>
+        <v>117.403003692627</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.07692307692308</v>
+        <v>1.111348947421401</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>1.538461538461542</v>
+        <v>1.587641353459146</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>18</v>
+        <v>148</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>15218.10021972656</v>
+        <v>15796.04049682617</v>
       </c>
       <c r="U22" s="8" t="n">
-        <v>40.42553191489361</v>
+        <v>69.6969696969697</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>27.65957446808511</v>
+        <v>48.48484848484848</v>
       </c>
       <c r="W22" s="5" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>0.7900909636607102</v>
+        <v>1.229769527097014</v>
       </c>
       <c r="Y22" s="8" t="n">
-        <v>60.81441684378656</v>
+        <v>54.82663292184034</v>
       </c>
       <c r="Z22" s="8" t="n">
-        <v>33.05681362018801</v>
+        <v>20.42492358220735</v>
       </c>
       <c r="AA22" s="8" t="n">
-        <v>7.828790512813259</v>
+        <v>4.753021505008639</v>
       </c>
       <c r="AB22" s="8" t="n">
-        <v>26.88729216512122</v>
+        <v>4.106522485095998</v>
       </c>
       <c r="AC22" s="8" t="n">
-        <v>9.984389070014643</v>
+        <v>38.25130515029611</v>
       </c>
       <c r="AD22" s="8" t="n">
-        <v>30.01215821167272</v>
+        <v>7.231388531647498</v>
       </c>
       <c r="AE22" s="8" t="n">
-        <v>-18.44795485411731</v>
-      </c>
-      <c r="AF22" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+        <v>-7.029616272036021</v>
+      </c>
+      <c r="AF22" s="6" t="inlineStr"/>
       <c r="AG22" s="6" t="inlineStr"/>
       <c r="AH22" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="AI22" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 40% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ22" s="7" t="inlineStr">
-        <is>
-          <t>RELAXED smallcap | Extended &gt;7% above EMA20 | High volatility | Volume below average</t>
-        </is>
-      </c>
-      <c r="AK22" s="7" t="inlineStr">
-        <is>
-          <t>[18 Oct 2026] Sejal Glass Q2FY27 results: Revenue up 33%, EBITDA margin hits 18.35% - scanx.trade | [19 Oct 2026] Sejal Glass: ਮੁਨਾਫੇ ਵਿੱਚ 77% ਦਾ ਵੱਡਾ ਉਛਾਲ! Q2 ਦੇ ਨਤੀਜਿਆਂ ਨੇ ਨਿਵੇਸ਼ਕਾਂ ਨੂੰ ਕੀਤਾ ਖੁਸ਼ - Whalesbook | [19 Oct 2026] Sejal Glass Maintains FY27 Revenue Growth Target Of 25-40% With 18% EBITDA Margin - Sahi</t>
-        </is>
-      </c>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 70% of similar setups</t>
+        </is>
+      </c>
+      <c r="AJ22" s="7" t="inlineStr"/>
+      <c r="AK22" s="7" t="inlineStr"/>
       <c r="AL22" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -4621,7 +4473,7 @@
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
@@ -4697,15 +4549,11 @@
       <c r="AE23" s="8" t="n">
         <v>-29.62700536508819</v>
       </c>
-      <c r="AF23" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+      <c r="AF23" s="6" t="inlineStr"/>
       <c r="AG23" s="6" t="inlineStr"/>
       <c r="AH23" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI23" s="7" t="inlineStr">
@@ -4718,11 +4566,7 @@
           <t>RELAXED smallcap | Weak trend (ADX&lt;20) | High volatility</t>
         </is>
       </c>
-      <c r="AK23" s="7" t="inlineStr">
-        <is>
-          <t>[20 Oct 2026] DCI Infotech &amp; Communication Holds Near ₹334 as Traders Eye Resistance Zone - Exhaustion Gap - https://www.siam.in/ | [20 Oct 2026] Dc Infotech And Communication Limited (DCI) share price — eduinvesting - Howl.link</t>
-        </is>
-      </c>
+      <c r="AK23" s="7" t="inlineStr"/>
       <c r="AL23" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -4735,18 +4579,22 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Global Education Limited</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr"/>
+          <t>Tata Consultancy Services Limited</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -4755,7 +4603,7 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
@@ -4763,100 +4611,92 @@
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>139.9499969482422</v>
+        <v>2530</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>139.9499969482422</v>
+        <v>2530</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>138.9923944832483</v>
+        <v>2535.833348876953</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>140.6497469329834</v>
+        <v>2571.299549560546</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>134.3150554656982</v>
+        <v>2416.617672947805</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>4.026396288259961</v>
+        <v>5.363039458512771</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>149.7464967346191</v>
+        <v>2732.316100664063</v>
       </c>
       <c r="P24" s="9" t="n">
-        <v>153.9449966430664</v>
+        <v>2808.923094140625</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>1.73852733284361</v>
+        <v>1.305230001410653</v>
       </c>
       <c r="R24" s="8" t="n">
-        <v>2.483610475490873</v>
+        <v>1.864614287729503</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>142</v>
+        <v>7</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>19872.89956665039</v>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v>68.29268292682927</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>58.53658536585365</v>
-      </c>
+        <v>17874.96514453125</v>
+      </c>
+      <c r="U24" s="6" t="inlineStr"/>
+      <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="5" t="n">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>0.6684238650117866</v>
+        <v>1.214822493810229</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>57.10809160291118</v>
+        <v>74.67168132512569</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>37.27602995292027</v>
+        <v>36.35685355358669</v>
       </c>
       <c r="AA24" s="8" t="n">
-        <v>3.89417221518495</v>
+        <v>3.007219505290843</v>
       </c>
       <c r="AB24" s="8" t="n">
-        <v>5.83831314387262</v>
+        <v>20.82895945624357</v>
       </c>
       <c r="AC24" s="8" t="n">
-        <v>36.17787439879634</v>
+        <v>13.40005151921497</v>
       </c>
       <c r="AD24" s="8" t="n">
-        <v>8.963179190424119</v>
+        <v>23.95382550279507</v>
       </c>
       <c r="AE24" s="8" t="n">
-        <v>-4.470991844203287</v>
-      </c>
-      <c r="AF24" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AG24" s="6" t="inlineStr"/>
+        <v>-22.62474610613426</v>
+      </c>
+      <c r="AF24" s="6" t="inlineStr"/>
+      <c r="AG24" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="AH24" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI24" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | ADX&gt;=25 strong trend | OBV rising | Near 52W high | Beating NIFTY 1M | Stock hit +7% in 15d 68% of similar setups</t>
+          <t>MACD bullish | ADX&gt;=25 strong trend | OBV rising | BB squeeze before move | Beating NIFTY 1M</t>
         </is>
       </c>
       <c r="AJ24" s="7" t="inlineStr">
         <is>
-          <t>Volume below average</t>
-        </is>
-      </c>
-      <c r="AK24" s="7" t="inlineStr">
-        <is>
-          <t>[21 Oct 2026] Virtual Global Education approves Q2FY27 results amid qualified audit opinion - scanx.trade | [21 Oct 2026] Virtual Global Education appoints Krishan Bansal as CFO and ED - scanx.trade</t>
-        </is>
-      </c>
+          <t>RELAXED smallcap | RSI&gt;70 (hot) | Extended &gt;7% above EMA20</t>
+        </is>
+      </c>
+      <c r="AK24" s="7" t="inlineStr"/>
       <c r="AL24" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -4976,7 +4816,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 23-Oct-2026 16:45 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
+          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 25-Oct-2026 21:21 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5054,7 @@
         <v>1076.228193316644</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>1017.323434543273</v>
+        <v>1017.32343541615</v>
       </c>
       <c r="I5" s="8" t="n">
         <v>66.7038465474425</v>
@@ -5244,7 +5084,7 @@
         <v>4.349230269942237</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>25.28574062184137</v>
+        <v>25.28650854698138</v>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
@@ -5252,13 +5092,13 @@
         </is>
       </c>
       <c r="T5" s="8" t="n">
-        <v>12.66882106476698</v>
+        <v>12.66911339435794</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>0.9825371938646775</v>
+        <v>0.9825371938647801</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>17.48678847231243</v>
+        <v>17.48678847230871</v>
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
@@ -5367,7 +5207,7 @@
         <v>4.255480954611603</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>4.717225503879559</v>
+        <v>4.717267838361655</v>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
@@ -5375,7 +5215,7 @@
         </is>
       </c>
       <c r="T6" s="8" t="n">
-        <v>10.25491926941226</v>
+        <v>10.25494066917044</v>
       </c>
       <c r="U6" s="8" t="n">
         <v>1.366849317269644</v>
@@ -5448,7 +5288,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>4751.10009765625</v>
@@ -5457,37 +5297,37 @@
         <v>4563.237599387827</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>4525.841850592878</v>
+        <v>4525.841850594383</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>4433.865331054128</v>
+        <v>4433.86533796789</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>62.38466863942166</v>
+        <v>62.38466863942168</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>23.49961741716015</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>-9.943303764956079</v>
+        <v>-9.943303764956097</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>33.44292118211623</v>
+        <v>33.44292118211625</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>14.69677073754477</v>
+        <v>14.69677073753119</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>23.65825087426195</v>
+        <v>23.65825087426283</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>11.04074675106886</v>
+        <v>11.04074675106903</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>147.069472986958</v>
+        <v>147.0694729869577</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>3.095482519080337</v>
+        <v>3.09548251908033</v>
       </c>
       <c r="R7" s="8" t="n">
         <v>1.886923235350515</v>
@@ -5501,10 +5341,10 @@
         <v>2.045497539921627</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>1.063418395098016</v>
+        <v>1.063418395098125</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>8.984112187523213</v>
+        <v>8.984112187521482</v>
       </c>
       <c r="W7" s="6" t="inlineStr">
         <is>
@@ -5571,49 +5411,49 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>2235</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>2157.470992502589</v>
+        <v>2157.470992502453</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>2136.537453055716</v>
+        <v>2136.537452912245</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1886.164499056871</v>
+        <v>1886.164496991822</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>63.91046213450047</v>
+        <v>63.91046213439159</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>11.27877325694681</v>
+        <v>11.27877325897498</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>-3.640103965102826</v>
+        <v>-3.640103962120766</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>14.91887722204963</v>
+        <v>14.91887722109575</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>26.7715343630463</v>
+        <v>26.77153440604747</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>23.94817001264243</v>
+        <v>23.94817001363672</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>19.13589995499332</v>
+        <v>19.13589995361283</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>49.92801118706748</v>
+        <v>49.92801118698427</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>2.23391548935425</v>
+        <v>2.233915489350526</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>2.075889578581005</v>
+        <v>2.075893436219113</v>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
@@ -5621,13 +5461,13 @@
         </is>
       </c>
       <c r="T8" s="8" t="n">
-        <v>4.127400160217147</v>
+        <v>4.127401995465102</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>1.026072354792677</v>
+        <v>1.02607235479233</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>8.765285775853128</v>
+        <v>8.765285775858906</v>
       </c>
       <c r="W8" s="6" t="inlineStr">
         <is>
@@ -5659,7 +5499,7 @@
         <v>-1.285902707469566</v>
       </c>
       <c r="AF8" s="8" t="n">
-        <v>3.593513320310304</v>
+        <v>3.59351332031681</v>
       </c>
       <c r="AG8" s="6" t="inlineStr">
         <is>
@@ -5736,7 +5576,7 @@
         <v>4.987176954740129</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>2.714630763344175</v>
+        <v>2.759638866068716</v>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
@@ -5744,7 +5584,7 @@
         </is>
       </c>
       <c r="T9" s="8" t="n">
-        <v>1.068539001456616</v>
+        <v>1.075523554994763</v>
       </c>
       <c r="U9" s="8" t="n">
         <v>0.970873860698974</v>
@@ -5826,10 +5666,10 @@
         <v>144.9842502395639</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>140.2140890059924</v>
+        <v>140.2140890059933</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>126.7447095370253</v>
+        <v>126.7447095317022</v>
       </c>
       <c r="I10" s="8" t="n">
         <v>62.12685793361327</v>
@@ -5859,7 +5699,7 @@
         <v>3.375935762306143</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>1.955010967917732</v>
+        <v>1.955119595771021</v>
       </c>
       <c r="S10" s="6" t="inlineStr">
         <is>
@@ -5867,13 +5707,13 @@
         </is>
       </c>
       <c r="T10" s="8" t="n">
-        <v>2.286762712952134</v>
+        <v>2.28671177846701</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>0.9271723990210601</v>
+        <v>0.927172399020867</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>13.50075571518397</v>
+        <v>13.50075571519007</v>
       </c>
       <c r="W10" s="6" t="inlineStr">
         <is>
@@ -5884,7 +5724,7 @@
         <v>75.91198690887539</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>75.52326153377761</v>
+        <v>75.52326153377763</v>
       </c>
       <c r="Z10" s="8" t="n">
         <v>-1.646149380871931</v>
@@ -5931,58 +5771,58 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>NEAR BREAKOUT</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>1790</v>
+        <v>781.75</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>1635.457667789009</v>
+        <v>742.9590054570057</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>1582.814209901726</v>
+        <v>731.6387175548579</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>1508.297426803757</v>
+        <v>710.0523417557914</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>71.66286040465398</v>
+        <v>65.33309839806414</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>64.22890719979728</v>
+        <v>11.91388977502686</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>28.85640475946043</v>
+        <v>5.579146340356273</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>35.37250244033685</v>
+        <v>6.334743434670587</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>27.18349324223552</v>
+        <v>19.92227355468049</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>40.85129822603346</v>
+        <v>29.35947900200509</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>10.20982710637033</v>
+        <v>12.39397869151918</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>53.50869515591368</v>
+        <v>21.05377926800627</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>2.989312578542664</v>
+        <v>2.693160123825554</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>0.8826152536772641</v>
+        <v>2.25349632206225</v>
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
@@ -5990,45 +5830,45 @@
         </is>
       </c>
       <c r="T11" s="8" t="n">
-        <v>2.788179452826085</v>
+        <v>1.772024429584253</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>0.8979722715373921</v>
+        <v>1.009469861545608</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>31.98700335876644</v>
+        <v>12.50096582199024</v>
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X11" s="8" t="n">
-        <v>86.72554513709325</v>
+        <v>85.09530082452068</v>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>94.33016185278132</v>
+        <v>78.93564764850812</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>-1.328481115168612</v>
+        <v>-0.07030395008957857</v>
       </c>
       <c r="AA11" s="8" t="n">
-        <v>9.381862623407876</v>
+        <v>5.435293968505062</v>
       </c>
       <c r="AB11" s="8" t="n">
-        <v>16.31869320425887</v>
+        <v>6.179966044142615</v>
       </c>
       <c r="AC11" s="8" t="n">
-        <v>16.00467509675574</v>
+        <v>7.969064730311093</v>
       </c>
       <c r="AD11" s="8" t="n">
-        <v>-2.131080108101291</v>
+        <v>-1.62335921698038</v>
       </c>
       <c r="AE11" s="8" t="n">
-        <v>-2.981029810298108</v>
+        <v>-1.62335921698038</v>
       </c>
       <c r="AF11" s="8" t="n">
-        <v>9.449485318682571</v>
+        <v>5.22114871185031</v>
       </c>
       <c r="AG11" s="6" t="inlineStr">
         <is>
@@ -6054,58 +5894,58 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
         <v>72</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>781.75</v>
+        <v>1790</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>742.9590054570057</v>
+        <v>1635.457667785497</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>731.6387175548579</v>
+        <v>1582.814209552523</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>710.0523417557914</v>
+        <v>1508.297424540518</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>65.33309839806414</v>
+        <v>71.66286037085388</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>11.91388977502686</v>
+        <v>64.2289072218623</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>5.579146340356273</v>
+        <v>28.85640479187514</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>6.334743434670587</v>
+        <v>35.37250242998716</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>19.92227355468049</v>
+        <v>27.18349290015075</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>29.35947900200509</v>
+        <v>40.85129826071311</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>12.39397869151918</v>
+        <v>10.20982714825877</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>21.05377926800627</v>
+        <v>53.50869518547744</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>2.693160123825554</v>
+        <v>2.98931258019427</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>2.253394665971034</v>
+        <v>0.8826221586172116</v>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
@@ -6113,45 +5953,45 @@
         </is>
       </c>
       <c r="T12" s="8" t="n">
-        <v>1.77206566433977</v>
+        <v>2.78817466775156</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>1.009469861545608</v>
+        <v>0.8979722715373939</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>12.50096582199024</v>
+        <v>31.98700335876629</v>
       </c>
       <c r="W12" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X12" s="8" t="n">
-        <v>85.09530082452068</v>
+        <v>86.72554513709325</v>
       </c>
       <c r="Y12" s="8" t="n">
-        <v>78.93564764850812</v>
+        <v>94.33016185278133</v>
       </c>
       <c r="Z12" s="8" t="n">
-        <v>-0.07030395008957857</v>
+        <v>-1.328481115168612</v>
       </c>
       <c r="AA12" s="8" t="n">
-        <v>5.435293968505062</v>
+        <v>9.381862623407876</v>
       </c>
       <c r="AB12" s="8" t="n">
-        <v>6.179966044142615</v>
+        <v>16.31869320425887</v>
       </c>
       <c r="AC12" s="8" t="n">
-        <v>7.969064730311093</v>
+        <v>16.00467509675574</v>
       </c>
       <c r="AD12" s="8" t="n">
-        <v>-1.62335921698038</v>
+        <v>-2.131080108101291</v>
       </c>
       <c r="AE12" s="8" t="n">
-        <v>-1.62335921698038</v>
+        <v>-2.981029810298108</v>
       </c>
       <c r="AF12" s="8" t="n">
-        <v>5.22114871185031</v>
+        <v>9.449485318917606</v>
       </c>
       <c r="AG12" s="6" t="inlineStr">
         <is>
@@ -6300,7 +6140,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -6312,46 +6152,46 @@
         <v>71</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>1475.599975585938</v>
+        <v>64.45999908447266</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>1451.159048201276</v>
+        <v>64.09230332545485</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>1403.280295353452</v>
+        <v>56.37276254360771</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>1155.763288289931</v>
+        <v>42.51732812971896</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>53.04321535619313</v>
+        <v>55.23144585056946</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>11.32989906680609</v>
+        <v>3.249740368486357</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>15.09119879548605</v>
+        <v>4.227797965648898</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>-3.761299728679957</v>
+        <v>-0.9780575971625414</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>21.35423501766923</v>
+        <v>56.04546748334655</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>25.20332806915918</v>
+        <v>22.20257567316706</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>18.37280648328698</v>
+        <v>34.09632368152246</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>83.04785834084117</v>
+        <v>4.346317966858813</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>5.628073984472938</v>
+        <v>6.74265905769423</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>2.040710687275184</v>
+        <v>2.386589512894483</v>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
@@ -6359,13 +6199,13 @@
         </is>
       </c>
       <c r="T14" s="8" t="n">
-        <v>2.275733369104918</v>
+        <v>3.254249349325946</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>0.6139553395699371</v>
+        <v>0.4701955359267601</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>17.41256236898882</v>
+        <v>28.33467777065835</v>
       </c>
       <c r="W14" s="6" t="inlineStr">
         <is>
@@ -6373,31 +6213,31 @@
         </is>
       </c>
       <c r="X14" s="8" t="n">
-        <v>49.57180899291582</v>
+        <v>56.87819764670645</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>43.08301009760668</v>
+        <v>39.79429484905824</v>
       </c>
       <c r="Z14" s="8" t="n">
-        <v>1.506502383549524</v>
+        <v>3.086519019435485</v>
       </c>
       <c r="AA14" s="8" t="n">
-        <v>2.188363960244977</v>
+        <v>-3.488548883240106</v>
       </c>
       <c r="AB14" s="8" t="n">
-        <v>6.005745372552984</v>
+        <v>10.018772685778</v>
       </c>
       <c r="AC14" s="8" t="n">
-        <v>21.29396186982777</v>
+        <v>99.47871438723736</v>
       </c>
       <c r="AD14" s="8" t="n">
-        <v>-9.400133859878835</v>
+        <v>-14.50928676394179</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>-12.0357689665611</v>
+        <v>-14.50928676394179</v>
       </c>
       <c r="AF14" s="8" t="n">
-        <v>1.684234916562466</v>
+        <v>0.5736972147040609</v>
       </c>
       <c r="AG14" s="6" t="inlineStr">
         <is>
@@ -6410,12 +6250,22 @@
       <c r="AI14" s="8" t="n">
         <v>-5.318897803699874</v>
       </c>
-      <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="6" t="inlineStr"/>
+      <c r="AJ14" s="5" t="n">
+        <v>2852.499456</v>
+      </c>
+      <c r="AK14" s="8" t="n">
+        <v>82.64103</v>
+      </c>
       <c r="AL14" s="6" t="inlineStr"/>
-      <c r="AM14" s="6" t="inlineStr"/>
-      <c r="AN14" s="6" t="inlineStr"/>
-      <c r="AO14" s="6" t="inlineStr"/>
+      <c r="AM14" s="8" t="n">
+        <v>0.05587</v>
+      </c>
+      <c r="AN14" s="8" t="n">
+        <v>336.3</v>
+      </c>
+      <c r="AO14" s="8" t="n">
+        <v>1400</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -6474,7 +6324,7 @@
         <v>3.868594740340416</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>1.125335025597956</v>
+        <v>1.125491610737459</v>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
@@ -6482,7 +6332,7 @@
         </is>
       </c>
       <c r="T15" s="8" t="n">
-        <v>3.831435359980372</v>
+        <v>3.831206521428958</v>
       </c>
       <c r="U15" s="8" t="n">
         <v>0.7468873797462584</v>
@@ -6546,7 +6396,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -6555,49 +6405,49 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>199.6600036621094</v>
+        <v>293</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>197.8206052040397</v>
+        <v>288.7450518283894</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>188.2377623915756</v>
+        <v>270.0156402584041</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>150.3794725662243</v>
+        <v>209.6311488459242</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>54.03760708213146</v>
+        <v>55.28912551064992</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>5.370834551162062</v>
+        <v>7.967892797126183</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>4.945565927554012</v>
+        <v>9.47930480669714</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.4252686236080496</v>
+        <v>-1.511412009570957</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>22.35732119485644</v>
+        <v>23.63393790269302</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>22.63535179339169</v>
+        <v>14.90121596392855</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>22.41083740803138</v>
+        <v>18.29520049847142</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>8.499247679277985</v>
+        <v>14.01843511302433</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>4.256860424415056</v>
+        <v>4.784448844035608</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>1.24518685503169</v>
+        <v>1.589543501505834</v>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
@@ -6605,45 +6455,45 @@
         </is>
       </c>
       <c r="T16" s="8" t="n">
-        <v>3.415775153713494</v>
+        <v>1.444687985082521</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>0.6026083118332035</v>
+        <v>0.5836173083608427</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>19.94683929215773</v>
+        <v>20.72033348450402</v>
       </c>
       <c r="W16" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X16" s="8" t="n">
-        <v>56.53099779256975</v>
+        <v>48.68587300108015</v>
       </c>
       <c r="Y16" s="8" t="n">
-        <v>64.55617175252426</v>
+        <v>43.69851365661005</v>
       </c>
       <c r="Z16" s="8" t="n">
-        <v>0.3972487375264233</v>
+        <v>-0.6779661016949157</v>
       </c>
       <c r="AA16" s="8" t="n">
-        <v>-5.798534306718583</v>
+        <v>-2.039453687407977</v>
       </c>
       <c r="AB16" s="8" t="n">
-        <v>5.333685279652012</v>
+        <v>8.901696076440846</v>
       </c>
       <c r="AC16" s="8" t="n">
-        <v>28.19261872366574</v>
+        <v>4.886134756224192</v>
       </c>
       <c r="AD16" s="8" t="n">
-        <v>-7.56481311939381</v>
+        <v>-6.539074960127589</v>
       </c>
       <c r="AE16" s="8" t="n">
-        <v>-7.56481311939381</v>
+        <v>-6.539074960127589</v>
       </c>
       <c r="AF16" s="8" t="n">
-        <v>0.9298315795629453</v>
+        <v>1.473600376757078</v>
       </c>
       <c r="AG16" s="6" t="inlineStr">
         <is>
@@ -6656,12 +6506,22 @@
       <c r="AI16" s="8" t="n">
         <v>-5.318897803699874</v>
       </c>
-      <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="6" t="inlineStr"/>
+      <c r="AJ16" s="5" t="n">
+        <v>2868.1422848</v>
+      </c>
+      <c r="AK16" s="8" t="n">
+        <v>9.512987000000001</v>
+      </c>
       <c r="AL16" s="6" t="inlineStr"/>
-      <c r="AM16" s="6" t="inlineStr"/>
-      <c r="AN16" s="6" t="inlineStr"/>
-      <c r="AO16" s="6" t="inlineStr"/>
+      <c r="AM16" s="8" t="n">
+        <v>0.22511</v>
+      </c>
+      <c r="AN16" s="8" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="AO16" s="8" t="n">
+        <v>633.1999999999999</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -6669,58 +6529,58 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>64.45999908447266</v>
+        <v>1046.849975585938</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>64.09230332545485</v>
+        <v>944.2173906971341</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>56.37276254360683</v>
+        <v>849.5456336476943</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>42.5173281232719</v>
+        <v>616.8659331444574</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>55.23144585056946</v>
+        <v>76.38632884606807</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>3.249740368486357</v>
+        <v>66.97576178968745</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>4.227797965648898</v>
+        <v>54.39232274774174</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>-0.9780575971625414</v>
+        <v>12.58343904194572</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>56.04546741086992</v>
+        <v>40.87138360524673</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>22.20257567161925</v>
+        <v>28.4373636543725</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>34.09632368307027</v>
+        <v>10.15691664203221</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>4.346317966858813</v>
+        <v>47.42870355306459</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>6.74265905769423</v>
+        <v>4.530611325325584</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>2.386415967260419</v>
+        <v>1.093507865595169</v>
       </c>
       <c r="S17" s="6" t="inlineStr">
         <is>
@@ -6728,13 +6588,13 @@
         </is>
       </c>
       <c r="T17" s="8" t="n">
-        <v>3.254120506495286</v>
+        <v>4.598031478707951</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>0.4701955359267529</v>
+        <v>0.8249604015144171</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>28.33467777065157</v>
+        <v>43.93499666950289</v>
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
@@ -6742,31 +6602,31 @@
         </is>
       </c>
       <c r="X17" s="8" t="n">
-        <v>56.87819764670645</v>
+        <v>86.25672076439227</v>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>39.79429484905825</v>
+        <v>86.8267357808043</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>3.086519019435485</v>
+        <v>0.3643091491229766</v>
       </c>
       <c r="AA17" s="8" t="n">
-        <v>-3.488548883240106</v>
+        <v>4.533422819462762</v>
       </c>
       <c r="AB17" s="8" t="n">
-        <v>10.018772685778</v>
+        <v>30.44046994066991</v>
       </c>
       <c r="AC17" s="8" t="n">
-        <v>99.47871438723736</v>
+        <v>61.25230374334849</v>
       </c>
       <c r="AD17" s="8" t="n">
-        <v>-14.50928676394179</v>
+        <v>-3.422664999046143</v>
       </c>
       <c r="AE17" s="8" t="n">
-        <v>-14.50928676394179</v>
+        <v>-3.422664999046143</v>
       </c>
       <c r="AF17" s="8" t="n">
-        <v>0.5736972147040609</v>
+        <v>10.8695927336212</v>
       </c>
       <c r="AG17" s="6" t="inlineStr">
         <is>
@@ -6779,12 +6639,22 @@
       <c r="AI17" s="8" t="n">
         <v>-5.318897803699874</v>
       </c>
-      <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="6" t="inlineStr"/>
+      <c r="AJ17" s="5" t="n">
+        <v>16212.9723392</v>
+      </c>
+      <c r="AK17" s="8" t="n">
+        <v>48.30872</v>
+      </c>
       <c r="AL17" s="6" t="inlineStr"/>
-      <c r="AM17" s="6" t="inlineStr"/>
-      <c r="AN17" s="6" t="inlineStr"/>
-      <c r="AO17" s="6" t="inlineStr"/>
+      <c r="AM17" s="8" t="n">
+        <v>0.72072</v>
+      </c>
+      <c r="AN17" s="8" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AO17" s="8" t="n">
+        <v>124.2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -6792,7 +6662,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>KRISHANA</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -6801,49 +6671,49 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>293</v>
+        <v>199.6600036621094</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>288.7450518283894</v>
+        <v>197.8206052040397</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>270.015640258381</v>
+        <v>188.2377623915703</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>209.6311488300422</v>
+        <v>150.3794725580886</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>55.28912551064992</v>
+        <v>54.03760708213146</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>7.967892797126183</v>
+        <v>5.370834551162062</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>9.47930480669714</v>
+        <v>4.945565927554012</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>-1.511412009570957</v>
+        <v>0.4252686236080496</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>23.63393790269321</v>
+        <v>22.35732119485634</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>14.90121596392855</v>
+        <v>22.63535179339169</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>18.29520049847141</v>
+        <v>22.41083740803138</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>14.01843511302433</v>
+        <v>8.499247679277985</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>4.784448844035608</v>
+        <v>4.256860424415056</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>1.589502479341174</v>
+        <v>1.245591049309489</v>
       </c>
       <c r="S18" s="6" t="inlineStr">
         <is>
@@ -6851,45 +6721,45 @@
         </is>
       </c>
       <c r="T18" s="8" t="n">
-        <v>1.444700621430397</v>
+        <v>3.415917027160998</v>
       </c>
       <c r="U18" s="8" t="n">
-        <v>0.5836173083608378</v>
+        <v>0.6026083118332035</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>20.72033348450524</v>
+        <v>19.94683929215773</v>
       </c>
       <c r="W18" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X18" s="8" t="n">
-        <v>48.68587300108015</v>
+        <v>56.53099779256975</v>
       </c>
       <c r="Y18" s="8" t="n">
-        <v>43.69851365661005</v>
+        <v>64.55617175252424</v>
       </c>
       <c r="Z18" s="8" t="n">
-        <v>-0.6779661016949157</v>
+        <v>0.3972487375264233</v>
       </c>
       <c r="AA18" s="8" t="n">
-        <v>-2.039453687407977</v>
+        <v>-5.798534306718583</v>
       </c>
       <c r="AB18" s="8" t="n">
-        <v>8.901696076440846</v>
+        <v>5.333685279652012</v>
       </c>
       <c r="AC18" s="8" t="n">
-        <v>4.886134756224192</v>
+        <v>28.19261872366574</v>
       </c>
       <c r="AD18" s="8" t="n">
-        <v>-6.539074960127589</v>
+        <v>-7.56481311939381</v>
       </c>
       <c r="AE18" s="8" t="n">
-        <v>-6.539074960127589</v>
+        <v>-7.56481311939381</v>
       </c>
       <c r="AF18" s="8" t="n">
-        <v>1.473600376757078</v>
+        <v>0.9298315795629453</v>
       </c>
       <c r="AG18" s="6" t="inlineStr">
         <is>
@@ -6915,58 +6785,58 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>MGEL</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>NEAR BREAKOUT</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>17.02000045776367</v>
+        <v>35.7599983215332</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>16.31183770833841</v>
+        <v>33.35316642386565</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>15.82858774047371</v>
+        <v>32.27581888738793</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>14.86552827110467</v>
+        <v>30.46823506293072</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>69.02241201590923</v>
+        <v>60.94981231881023</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.4185219009266774</v>
+        <v>1.555318736845322</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.3200951917839516</v>
+        <v>0.9842119515478512</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.09842670914272578</v>
+        <v>0.5711067852974711</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>24.63349883425135</v>
+        <v>27.0621664887438</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>17.50001372538278</v>
+        <v>20.03727493128024</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>11.81035134407579</v>
+        <v>13.30932313349743</v>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0.7323346875054594</v>
+        <v>2.144852759076529</v>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>4.302788882543214</v>
+        <v>5.997910681626029</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>1.1695111286998</v>
+        <v>0.8027997887424463</v>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
@@ -6974,45 +6844,45 @@
         </is>
       </c>
       <c r="T19" s="8" t="n">
-        <v>1.748613078908185</v>
+        <v>1.797230160165263</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>0.8627852231569582</v>
+        <v>0.757693057342725</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>14.05077079993208</v>
+        <v>44.24591170034879</v>
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" s="8" t="n">
-        <v>77.03351640228443</v>
+        <v>81.00508485425682</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>79.12611182788856</v>
+        <v>85.45612418956409</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>-0.05872124767251075</v>
+        <v>-3.585877124785852</v>
       </c>
       <c r="AA19" s="8" t="n">
-        <v>0.8891500359705429</v>
+        <v>7.001796172335739</v>
       </c>
       <c r="AB19" s="8" t="n">
-        <v>9.6649481685398</v>
+        <v>22.54968453578221</v>
       </c>
       <c r="AC19" s="8" t="n">
-        <v>4.097859698237616</v>
+        <v>4.074498504985091</v>
       </c>
       <c r="AD19" s="8" t="n">
-        <v>-2.742854527064731</v>
+        <v>-5.86997435748361</v>
       </c>
       <c r="AE19" s="8" t="n">
-        <v>-2.742854527064731</v>
+        <v>-5.86997435748361</v>
       </c>
       <c r="AF19" s="8" t="n">
-        <v>4.341403844787273</v>
+        <v>7.216202105313019</v>
       </c>
       <c r="AG19" s="6" t="inlineStr">
         <is>
@@ -7025,12 +6895,22 @@
       <c r="AI19" s="8" t="n">
         <v>-5.318897803699874</v>
       </c>
-      <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="6" t="inlineStr"/>
-      <c r="AL19" s="6" t="inlineStr"/>
+      <c r="AJ19" s="5" t="n">
+        <v>1411.4429952</v>
+      </c>
+      <c r="AK19" s="8" t="n">
+        <v>12.204778</v>
+      </c>
+      <c r="AL19" s="8" t="n">
+        <v>7.915</v>
+      </c>
       <c r="AM19" s="6" t="inlineStr"/>
-      <c r="AN19" s="6" t="inlineStr"/>
-      <c r="AO19" s="6" t="inlineStr"/>
+      <c r="AN19" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO19" s="8" t="n">
+        <v>103.2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -7038,58 +6918,58 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>EMA20 PULLBACK</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>35.7599983215332</v>
+        <v>1475.599975585938</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>33.35316642386565</v>
+        <v>1451.159048201276</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>32.27581888738793</v>
+        <v>1403.280295353452</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>30.46823506293072</v>
+        <v>1155.763288289931</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>60.94981231881023</v>
+        <v>53.04321535619313</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1.555318736845322</v>
+        <v>11.32989906680609</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.9842119515478512</v>
+        <v>15.09119879548605</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.5711067852974711</v>
+        <v>-3.761299728679957</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>27.0621664887438</v>
+        <v>21.35423501766923</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>20.03727493128024</v>
+        <v>25.20332806915918</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>13.30932313349743</v>
+        <v>18.37280648328698</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>2.144852759076529</v>
+        <v>83.04785834084117</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>5.997910681626029</v>
+        <v>5.628073984472938</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>0.8027965940661571</v>
+        <v>2.041127583077954</v>
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
@@ -7097,13 +6977,13 @@
         </is>
       </c>
       <c r="T20" s="8" t="n">
-        <v>1.797231994145078</v>
+        <v>2.275886325349501</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>0.757693057342725</v>
+        <v>0.6139553395699371</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>44.24591170034879</v>
+        <v>17.41256236898882</v>
       </c>
       <c r="W20" s="6" t="inlineStr">
         <is>
@@ -7111,31 +6991,31 @@
         </is>
       </c>
       <c r="X20" s="8" t="n">
-        <v>81.00508485425682</v>
+        <v>49.57180899291582</v>
       </c>
       <c r="Y20" s="8" t="n">
-        <v>85.45612418956409</v>
+        <v>43.08301009760668</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>-3.585877124785852</v>
+        <v>1.506502383549524</v>
       </c>
       <c r="AA20" s="8" t="n">
-        <v>7.001796172335739</v>
+        <v>2.188363960244977</v>
       </c>
       <c r="AB20" s="8" t="n">
-        <v>22.54968453578221</v>
+        <v>6.005745372552984</v>
       </c>
       <c r="AC20" s="8" t="n">
-        <v>4.074498504985091</v>
+        <v>21.29396186982777</v>
       </c>
       <c r="AD20" s="8" t="n">
-        <v>-5.86997435748361</v>
+        <v>-9.400133859878835</v>
       </c>
       <c r="AE20" s="8" t="n">
-        <v>-5.86997435748361</v>
+        <v>-12.0357689665611</v>
       </c>
       <c r="AF20" s="8" t="n">
-        <v>7.216202105313019</v>
+        <v>1.684234916562466</v>
       </c>
       <c r="AG20" s="6" t="inlineStr">
         <is>
@@ -7161,58 +7041,58 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>MGEL</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>1046.849975585938</v>
+        <v>17.02000045776367</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>944.2173906971341</v>
+        <v>16.31183770833841</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>849.5456336476943</v>
+        <v>15.82858774047347</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>616.8659331444574</v>
+        <v>14.86552826463018</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>76.38632884606807</v>
+        <v>69.02241201590923</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>66.97576178968745</v>
+        <v>0.4185219009266774</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>54.39232274774174</v>
+        <v>0.3200951917839516</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>12.58343904194572</v>
+        <v>0.09842670914272578</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>40.87138360524673</v>
+        <v>24.63349883425135</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>28.4373636543725</v>
+        <v>17.50001372538278</v>
       </c>
       <c r="O21" s="8" t="n">
-        <v>10.15691664203221</v>
+        <v>11.81035134407579</v>
       </c>
       <c r="P21" s="9" t="n">
-        <v>47.42870355306459</v>
+        <v>0.7323346875054594</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>4.530611325325584</v>
+        <v>4.302788882543214</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>1.093398314519418</v>
+        <v>1.1695111286998</v>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
@@ -7220,45 +7100,45 @@
         </is>
       </c>
       <c r="T21" s="8" t="n">
-        <v>4.597980139535034</v>
+        <v>1.748613078908185</v>
       </c>
       <c r="U21" s="8" t="n">
-        <v>0.8249604015144171</v>
+        <v>0.8627852231570816</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>43.93499666950289</v>
+        <v>14.0507707999273</v>
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X21" s="8" t="n">
-        <v>86.25672076439227</v>
+        <v>77.03351640228443</v>
       </c>
       <c r="Y21" s="8" t="n">
-        <v>86.8267357808043</v>
+        <v>79.12611182788861</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>0.3643091491229766</v>
+        <v>-0.05872124767251075</v>
       </c>
       <c r="AA21" s="8" t="n">
-        <v>4.533422819462762</v>
+        <v>0.8891500359705429</v>
       </c>
       <c r="AB21" s="8" t="n">
-        <v>30.44046994066991</v>
+        <v>9.6649481685398</v>
       </c>
       <c r="AC21" s="8" t="n">
-        <v>61.25230374334849</v>
+        <v>4.097859698237616</v>
       </c>
       <c r="AD21" s="8" t="n">
-        <v>-3.422664999046143</v>
+        <v>-2.742854527064731</v>
       </c>
       <c r="AE21" s="8" t="n">
-        <v>-3.422664999046143</v>
+        <v>-2.742854527064731</v>
       </c>
       <c r="AF21" s="8" t="n">
-        <v>10.8695927336212</v>
+        <v>4.341403844787273</v>
       </c>
       <c r="AG21" s="6" t="inlineStr">
         <is>
@@ -7293,7 +7173,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>243.9100036621094</v>
@@ -7335,7 +7215,7 @@
         <v>3.916215694288921</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>1.006830215370086</v>
+        <v>1.007296015434859</v>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
@@ -7343,7 +7223,7 @@
         </is>
       </c>
       <c r="T22" s="8" t="n">
-        <v>1.695283063328895</v>
+        <v>1.695393296391944</v>
       </c>
       <c r="U22" s="8" t="n">
         <v>0.72941286787741</v>
@@ -7394,12 +7274,22 @@
       <c r="AI22" s="8" t="n">
         <v>-5.318897803699874</v>
       </c>
-      <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="6" t="inlineStr"/>
+      <c r="AJ22" s="5" t="n">
+        <v>440.2267136</v>
+      </c>
+      <c r="AK22" s="8" t="n">
+        <v>21.855736</v>
+      </c>
       <c r="AL22" s="6" t="inlineStr"/>
-      <c r="AM22" s="6" t="inlineStr"/>
-      <c r="AN22" s="6" t="inlineStr"/>
-      <c r="AO22" s="6" t="inlineStr"/>
+      <c r="AM22" s="8" t="n">
+        <v>2.03436</v>
+      </c>
+      <c r="AN22" s="8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AO22" s="8" t="n">
+        <v>11.4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -7416,7 +7306,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>540</v>
@@ -7517,12 +7407,22 @@
       <c r="AI23" s="8" t="n">
         <v>-5.318897803699874</v>
       </c>
-      <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="6" t="inlineStr"/>
+      <c r="AJ23" s="5" t="n">
+        <v>734.4216064</v>
+      </c>
+      <c r="AK23" s="8" t="n">
+        <v>102.0794</v>
+      </c>
       <c r="AL23" s="6" t="inlineStr"/>
-      <c r="AM23" s="6" t="inlineStr"/>
-      <c r="AN23" s="6" t="inlineStr"/>
-      <c r="AO23" s="6" t="inlineStr"/>
+      <c r="AM23" s="8" t="n">
+        <v>0.80361</v>
+      </c>
+      <c r="AN23" s="8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AO23" s="8" t="n">
+        <v>149.1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -7539,7 +7439,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>86.04000091552734</v>
@@ -7641,8 +7541,12 @@
       <c r="AJ24" s="6" t="inlineStr"/>
       <c r="AK24" s="6" t="inlineStr"/>
       <c r="AL24" s="6" t="inlineStr"/>
-      <c r="AM24" s="6" t="inlineStr"/>
-      <c r="AN24" s="6" t="inlineStr"/>
+      <c r="AM24" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="AN24" s="8" t="n">
+        <v>56.89999999999999</v>
+      </c>
       <c r="AO24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
@@ -7651,7 +7555,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>AAREYDRUGS</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -7660,63 +7564,63 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>106.7300033569336</v>
+        <v>1900.5</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>106.0287253175297</v>
+        <v>1880.723140871288</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>99.09982531265351</v>
+        <v>1824.94322793876</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>85.22481228584229</v>
+        <v>1644.736517130493</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>54.82663292184034</v>
+        <v>54.55287821241041</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>3.609737525462407</v>
+        <v>28.23245673632664</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>3.780559408821775</v>
+        <v>21.94042464933815</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>-0.170821883359368</v>
+        <v>6.292032086988485</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>20.42492358220735</v>
+        <v>16.96824002509117</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>17.74978149198301</v>
+        <v>15.10842189939252</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>14.88824718185496</v>
+        <v>14.99940216240613</v>
       </c>
       <c r="P25" s="9" t="n">
-        <v>5.072900011851496</v>
+        <v>62.99282024060134</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>4.753021505008639</v>
+        <v>3.314539344414698</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>1.229769527097014</v>
+        <v>1.642262016726502</v>
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>Rising</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
-        <v>1.270757144293763</v>
+        <v>1.03907094769382</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>0.5563142045441768</v>
+        <v>0.6572579360679321</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>16.27825007775939</v>
+        <v>15.22542522815168</v>
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
@@ -7724,31 +7628,31 @@
         </is>
       </c>
       <c r="X25" s="8" t="n">
-        <v>43.56644774399386</v>
+        <v>53.72606459647029</v>
       </c>
       <c r="Y25" s="8" t="n">
-        <v>64.81536325629635</v>
+        <v>70.07900967041989</v>
       </c>
       <c r="Z25" s="8" t="n">
-        <v>-3.333031594164038</v>
+        <v>-0.4348307112219896</v>
       </c>
       <c r="AA25" s="8" t="n">
-        <v>-1.848440818763009</v>
+        <v>-1.747404641208705</v>
       </c>
       <c r="AB25" s="8" t="n">
-        <v>4.106522485095998</v>
+        <v>5.407653910149746</v>
       </c>
       <c r="AC25" s="8" t="n">
-        <v>38.25130515029611</v>
+        <v>32.29581811051689</v>
       </c>
       <c r="AD25" s="8" t="n">
-        <v>-7.029616272036021</v>
+        <v>-4.334036879293867</v>
       </c>
       <c r="AE25" s="8" t="n">
-        <v>-7.029616272036021</v>
+        <v>-5.971697708675194</v>
       </c>
       <c r="AF25" s="8" t="n">
-        <v>0.66140381986457</v>
+        <v>1.051556111525764</v>
       </c>
       <c r="AG25" s="6" t="inlineStr">
         <is>
@@ -7761,12 +7665,24 @@
       <c r="AI25" s="8" t="n">
         <v>-5.318897803699874</v>
       </c>
-      <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="6" t="inlineStr"/>
-      <c r="AL25" s="6" t="inlineStr"/>
-      <c r="AM25" s="6" t="inlineStr"/>
-      <c r="AN25" s="6" t="inlineStr"/>
-      <c r="AO25" s="6" t="inlineStr"/>
+      <c r="AJ25" s="5" t="n">
+        <v>84199.4928128</v>
+      </c>
+      <c r="AK25" s="8" t="n">
+        <v>37.28664</v>
+      </c>
+      <c r="AL25" s="8" t="n">
+        <v>13.347</v>
+      </c>
+      <c r="AM25" s="8" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="AN25" s="8" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AO25" s="8" t="n">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -7774,104 +7690,104 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>SEJALLTD</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>1900.5</v>
+        <v>845.4500122070312</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1880.723140871288</v>
+        <v>775.2241688280454</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>1824.943227929418</v>
+        <v>731.0203677827178</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>1644.736516560049</v>
+        <v>703.9386770469583</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>54.55287821242818</v>
+        <v>60.81441684378656</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>28.23245673634483</v>
+        <v>50.97414837644658</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>21.94042464936452</v>
+        <v>36.50969317156498</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>6.292032086980306</v>
+        <v>14.4644552048816</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>16.96824002595774</v>
+        <v>33.05681362018801</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>15.10842189935576</v>
+        <v>32.34636824860602</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>14.99940216235668</v>
+        <v>16.59203991609472</v>
       </c>
       <c r="P26" s="9" t="n">
-        <v>62.99282024056036</v>
+        <v>66.18851034624261</v>
       </c>
       <c r="Q26" s="8" t="n">
-        <v>3.314539344412542</v>
+        <v>7.828790512813259</v>
       </c>
       <c r="R26" s="8" t="n">
-        <v>1.642165566809154</v>
+        <v>0.7908182112019209</v>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Rising</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
-        <v>1.039088419496409</v>
+        <v>3.077742587981207</v>
       </c>
       <c r="U26" s="8" t="n">
-        <v>0.6572579360679933</v>
+        <v>0.746586673007816</v>
       </c>
       <c r="V26" s="8" t="n">
-        <v>15.22542522814576</v>
+        <v>54.28443385943575</v>
       </c>
       <c r="W26" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X26" s="8" t="n">
-        <v>53.72606459647029</v>
+        <v>53.67590225528271</v>
       </c>
       <c r="Y26" s="8" t="n">
-        <v>70.07900967041986</v>
+        <v>54.82354106034418</v>
       </c>
       <c r="Z26" s="8" t="n">
-        <v>-0.4348307112219896</v>
+        <v>-2.248816239796958</v>
       </c>
       <c r="AA26" s="8" t="n">
-        <v>-1.747404641208705</v>
+        <v>-12.49288507550695</v>
       </c>
       <c r="AB26" s="8" t="n">
-        <v>5.407653910149746</v>
+        <v>26.88729216512122</v>
       </c>
       <c r="AC26" s="8" t="n">
-        <v>32.29581811051689</v>
+        <v>9.984389070014643</v>
       </c>
       <c r="AD26" s="8" t="n">
-        <v>-4.334036879293867</v>
+        <v>-17.46876297756702</v>
       </c>
       <c r="AE26" s="8" t="n">
-        <v>-5.971697708675194</v>
+        <v>-18.44795485411731</v>
       </c>
       <c r="AF26" s="8" t="n">
-        <v>1.051556111525809</v>
+        <v>9.058778892968554</v>
       </c>
       <c r="AG26" s="6" t="inlineStr">
         <is>
@@ -7884,12 +7800,24 @@
       <c r="AI26" s="8" t="n">
         <v>-5.318897803699874</v>
       </c>
-      <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="6" t="inlineStr"/>
-      <c r="AL26" s="6" t="inlineStr"/>
-      <c r="AM26" s="6" t="inlineStr"/>
-      <c r="AN26" s="6" t="inlineStr"/>
-      <c r="AO26" s="6" t="inlineStr"/>
+      <c r="AJ26" s="5" t="n">
+        <v>991.2245248</v>
+      </c>
+      <c r="AK26" s="8" t="n">
+        <v>25.681957</v>
+      </c>
+      <c r="AL26" s="8" t="n">
+        <v>33.103</v>
+      </c>
+      <c r="AM26" s="8" t="n">
+        <v>1.20385</v>
+      </c>
+      <c r="AN26" s="8" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AO26" s="8" t="n">
+        <v>52.2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -7897,58 +7825,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>SEJALLTD</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>EMA20 PULLBACK</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>845.4500122070312</v>
+        <v>106.7300033569336</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>775.2241688280454</v>
+        <v>106.0287253175297</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>731.0203677827178</v>
+        <v>99.09982531265351</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>703.9386770469583</v>
+        <v>85.22481228584229</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>60.81441684378656</v>
+        <v>54.82663292184034</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>50.97414837644658</v>
+        <v>3.609737525462407</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>36.50969317156498</v>
+        <v>3.780559408821775</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>14.4644552048816</v>
+        <v>-0.170821883359368</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>33.05681362018801</v>
+        <v>20.42492358220735</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>32.34636824860602</v>
+        <v>17.74978149198301</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>16.59203991609472</v>
+        <v>14.88824718185496</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>66.18851034624261</v>
+        <v>5.072900011851496</v>
       </c>
       <c r="Q27" s="8" t="n">
-        <v>7.828790512813259</v>
+        <v>4.753021505008639</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>0.7900909636607102</v>
+        <v>1.229769527097014</v>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
@@ -7956,45 +7884,45 @@
         </is>
       </c>
       <c r="T27" s="8" t="n">
-        <v>3.078263532901312</v>
+        <v>1.270757144293763</v>
       </c>
       <c r="U27" s="8" t="n">
-        <v>0.746586673007816</v>
+        <v>0.5563142045441768</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>54.28443385943575</v>
+        <v>16.27825007775939</v>
       </c>
       <c r="W27" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X27" s="8" t="n">
-        <v>53.67590225528271</v>
+        <v>43.56644774399386</v>
       </c>
       <c r="Y27" s="8" t="n">
-        <v>54.82354106034418</v>
+        <v>64.81536325629635</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>-2.248816239796958</v>
+        <v>-3.333031594164038</v>
       </c>
       <c r="AA27" s="8" t="n">
-        <v>-12.49288507550695</v>
+        <v>-1.848440818763009</v>
       </c>
       <c r="AB27" s="8" t="n">
-        <v>26.88729216512122</v>
+        <v>4.106522485095998</v>
       </c>
       <c r="AC27" s="8" t="n">
-        <v>9.984389070014643</v>
+        <v>38.25130515029611</v>
       </c>
       <c r="AD27" s="8" t="n">
-        <v>-17.46876297756702</v>
+        <v>-7.029616272036021</v>
       </c>
       <c r="AE27" s="8" t="n">
-        <v>-18.44795485411731</v>
+        <v>-7.029616272036021</v>
       </c>
       <c r="AF27" s="8" t="n">
-        <v>9.058778892968554</v>
+        <v>0.66140381986457</v>
       </c>
       <c r="AG27" s="6" t="inlineStr">
         <is>
@@ -8007,12 +7935,22 @@
       <c r="AI27" s="8" t="n">
         <v>-5.318897803699874</v>
       </c>
-      <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="6" t="inlineStr"/>
+      <c r="AJ27" s="5" t="n">
+        <v>340.1944576</v>
+      </c>
+      <c r="AK27" s="8" t="n">
+        <v>72.605446</v>
+      </c>
       <c r="AL27" s="6" t="inlineStr"/>
-      <c r="AM27" s="6" t="inlineStr"/>
-      <c r="AN27" s="6" t="inlineStr"/>
-      <c r="AO27" s="6" t="inlineStr"/>
+      <c r="AM27" s="8" t="n">
+        <v>0.40385</v>
+      </c>
+      <c r="AN27" s="8" t="n">
+        <v>-56.3</v>
+      </c>
+      <c r="AO27" s="8" t="n">
+        <v>-25</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -8029,7 +7967,7 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>334.1499938964844</v>
@@ -8130,12 +8068,22 @@
       <c r="AI28" s="8" t="n">
         <v>-5.318897803699874</v>
       </c>
-      <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="6" t="inlineStr"/>
+      <c r="AJ28" s="5" t="n">
+        <v>548.0059904</v>
+      </c>
+      <c r="AK28" s="8" t="n">
+        <v>25.048725</v>
+      </c>
       <c r="AL28" s="6" t="inlineStr"/>
-      <c r="AM28" s="6" t="inlineStr"/>
-      <c r="AN28" s="6" t="inlineStr"/>
-      <c r="AO28" s="6" t="inlineStr"/>
+      <c r="AM28" s="8" t="n">
+        <v>0.80889</v>
+      </c>
+      <c r="AN28" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AO28" s="8" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -8143,58 +8091,58 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>139.9499969482422</v>
+        <v>2530</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>138.9923944832483</v>
+        <v>2299.214286675739</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>129.083695254677</v>
+        <v>2249.933157280451</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>107.1596877146587</v>
+        <v>2419.867105793944</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>57.10809160291118</v>
+        <v>74.67168132512569</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>4.467323431530616</v>
+        <v>87.88144188512433</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>5.519568735682105</v>
+        <v>37.65808660656754</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>-1.052245304151489</v>
+        <v>50.2233552785568</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>37.27602995292027</v>
+        <v>36.35685355358669</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>16.38657636522334</v>
+        <v>41.3549520132809</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>19.13144111104945</v>
+        <v>7.981177838555893</v>
       </c>
       <c r="P29" s="9" t="n">
-        <v>5.449893896310633</v>
+        <v>76.08265348385832</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>3.89417221518495</v>
+        <v>3.007219505290843</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>0.6684238650117866</v>
+        <v>1.214822493810229</v>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
@@ -8202,45 +8150,45 @@
         </is>
       </c>
       <c r="T29" s="8" t="n">
-        <v>1.661726436556945</v>
+        <v>4.195371925088065</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>0.4750613417744807</v>
+        <v>0.9159713808203066</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>11.18598847620508</v>
+        <v>34.0582416892805</v>
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X29" s="8" t="n">
-        <v>43.09290896822166</v>
+        <v>83.50388510277867</v>
       </c>
       <c r="Y29" s="8" t="n">
-        <v>64.44373039193034</v>
+        <v>92.45057286778399</v>
       </c>
       <c r="Z29" s="8" t="n">
-        <v>-1.789475825794962</v>
+        <v>0.9214607106830641</v>
       </c>
       <c r="AA29" s="8" t="n">
-        <v>-3.148791039278764</v>
+        <v>7.659574468085117</v>
       </c>
       <c r="AB29" s="8" t="n">
-        <v>5.83831314387262</v>
+        <v>20.82895945624357</v>
       </c>
       <c r="AC29" s="8" t="n">
-        <v>36.17787439879634</v>
+        <v>13.40005151921497</v>
       </c>
       <c r="AD29" s="8" t="n">
-        <v>-4.470991844203287</v>
+        <v>-0.130266796846723</v>
       </c>
       <c r="AE29" s="8" t="n">
-        <v>-4.470991844203287</v>
+        <v>-22.62474610613426</v>
       </c>
       <c r="AF29" s="8" t="n">
-        <v>0.6889603338039452</v>
+        <v>10.03759043520633</v>
       </c>
       <c r="AG29" s="6" t="inlineStr">
         <is>
@@ -8254,11 +8202,21 @@
         <v>-5.318897803699874</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="6" t="inlineStr"/>
-      <c r="AL29" s="6" t="inlineStr"/>
-      <c r="AM29" s="6" t="inlineStr"/>
-      <c r="AN29" s="6" t="inlineStr"/>
-      <c r="AO29" s="6" t="inlineStr"/>
+      <c r="AK29" s="8" t="n">
+        <v>17.734472</v>
+      </c>
+      <c r="AL29" s="8" t="n">
+        <v>45.573002</v>
+      </c>
+      <c r="AM29" s="8" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="AN29" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AO29" s="8" t="n">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:AO29"/>
@@ -8284,7 +8242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -8422,7 +8380,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rejected - extended/spiking (even relaxed): 8</t>
+          <t xml:space="preserve">   rejected - extended/spiking (even relaxed): 7</t>
         </is>
       </c>
     </row>
@@ -8450,99 +8408,106 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 33, RVOL 0.20): 1</t>
+          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 36, RVOL 0.36): 1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rejected - ATR% outside relaxed band: 2</t>
+          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 33, RVOL 0.20): 1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 39, RVOL 0.49): 1</t>
+          <t xml:space="preserve">   rejected - ATR% outside relaxed band: 2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 52, RVOL 0.32): 1</t>
+          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 39, RVOL 0.49): 1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 48, RVOL 0.13): 1</t>
+          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 52, RVOL 0.32): 1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 20, RVOL 0.40): 1</t>
+          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 48, RVOL 0.13): 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 22, RVOL 0.38): 1</t>
+          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 20, RVOL 0.40): 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 37, RVOL 0.40): 1</t>
+          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 22, RVOL 0.38): 1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 46, RVOL 0.32): 1</t>
+          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 37, RVOL 0.40): 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>3. Passed technical filters: 63</t>
+          <t xml:space="preserve">   rejected - ADX/RVOL weak (relaxed: ADX 46, RVOL 0.32): 1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>4. Shortlisted for news/fundamentals: 45</t>
+          <t>3. Passed technical filters: 63</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>5. Final SWING PICKS: 5</t>
+          <t>4. Shortlisted for news/fundamentals: 45</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
+          <t>5. Final SWING PICKS: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
           <t>6. WATCHLIST: 20</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr"/>
-    </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>If too few stocks qualify, relax in CONFIG: MIN_SCORE (60-&gt;55), RSI_MIN, ADX_MIN, ATR_PCT_MIN, or use --universe NIFTY500.</t>
         </is>
